--- a/Översikt ALINGSÅS.xlsx
+++ b/Översikt ALINGSÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46036</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45091</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45243</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45249</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45630</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44621</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44868</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45274</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>45279</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>44803</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>46275</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>45274</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>45630</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>45240</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>45442</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>46189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>46275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45279</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45630</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>46044</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>46245</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45607</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45483</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>45640</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>45889</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>45271</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45812</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>45330</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>46044</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>46108</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>45607</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45541</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>45366</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>44628</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>44614</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44831</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>44754</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>44637</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>44708</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>44817</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>44516</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>44852</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>44773</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>44809</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>44572</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>44652</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>44510</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>44515</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>44496</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>44536</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>44461</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>44568</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>44809</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>44582</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>44719</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>44795</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>44642</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>44726</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45634</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>45456</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>45118</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>44991</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>44903</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>44582</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>45660</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>45210</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>45465</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>45637</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>45617</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>44979</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>45329</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>45576</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>45097</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>45608</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>45608</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>45568</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>45465</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>45015</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>45254</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         <v>45534</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>44461</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>45335</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>45335</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>45679</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>45111</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>45196</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>44991</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>44977</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>44631</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>45406</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44488</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>45687</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>45356</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>45261</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>44949</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>44505</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>45230</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>44727</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>45329</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>45681</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>45512</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>45468</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>44979</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>44896</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>45792</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>44964</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>45219</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>45465</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>45465</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>45915</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>45894</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>44896</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>45826</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>45782</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>45894</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>45772</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>45901</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>45901</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>45681</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>45905</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>45133</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>45908</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>45908</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         <v>45908</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>45910</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>44984</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11427,7 +11427,7 @@
         <v>44974</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
         <v>45841</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>45916</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>44596</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45922</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>45244</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>45600</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>45929</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>45931</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>45279</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>44672</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>44672</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>45279</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45279</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>45257</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>45937</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>45937</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>45938</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>44615</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>44832</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>45722</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>44729</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>45922</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>45371</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>45427</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45412</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45310</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>45958</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45958</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>45964</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>45964</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>45964</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>44821</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>44469</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>45966</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
         <v>45966</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>45420</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>45969</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>45972</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>45380</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>45972</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>45974</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>45973</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>45973</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>44727</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         <v>45257</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>45986</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>45785</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>45989</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>45989</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>44721</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>45265</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>45596</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>45399</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>45996</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>46000</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>46000</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>45589</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>44831</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>44708</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>45075</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>46008</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>44957</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>45608</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>46014</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>46014</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>45708</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>45708</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>45699</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45021</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>45271</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>44852</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>45166</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>46035</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>46174</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>46174</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>46171</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>46038</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>44964</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>46038</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>46038</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>45391</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         <v>46038</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>46174</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>45152</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>46044</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>46176</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>46176</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>46176</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17949,7 +17949,7 @@
         <v>46177</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44953</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>46177</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>46177</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         <v>46177</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>46178</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>46070</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>45569</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         <v>45378</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>44855</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         <v>46086</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>46086</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>46185</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         <v>46189</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>46189</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>45349</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>45091</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>46191</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>46191</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>45546</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>46107</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>46108</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>46108</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>46107</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>45576</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>46108</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>45011</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>44907</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>46245</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>46245</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>44637</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>45608</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>46122</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>46121</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>46121</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>46126</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>46129</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>45156</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>46127</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>45465</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>46131</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>45630</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>44949</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21098,7 +21098,7 @@
         <v>45440</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>45271</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>45015</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21317,7 +21317,7 @@
         <v>44977</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>45258</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>45166</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>46246</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>46248</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>46248</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>44816</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>45173</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>46255</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>45706</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22047,7 +22047,7 @@
         <v>45465</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>45429</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>46262</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>45177</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>45594</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22412,7 +22412,7 @@
         <v>46266</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>45721</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>46232</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>45519</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22704,7 +22704,7 @@
         <v>45792</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>46282</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22850,7 +22850,7 @@
         <v>45681</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>45510</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>45258</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>45803</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>45805</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>45804</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>45804</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23361,7 +23361,7 @@
         <v>45617</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>45734</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>45378</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>45812</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>45818</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>45721</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>45726</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>45726</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>45726</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>45726</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>45716</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>45429</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45850</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>45253</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45850</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45757</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>45323</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>45323</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>45355</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>45429</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>45552</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>44804</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>45323</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25045,7 +25045,7 @@
         <v>45355</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>45813</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>45010</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>

--- a/Översikt ALINGSÅS.xlsx
+++ b/Översikt ALINGSÅS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE320"/>
+  <dimension ref="A1:AE313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46036</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45091</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45243</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45249</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45630</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44621</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44868</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45274</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>45279</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>44803</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>46275</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>45274</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>45630</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>45240</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 21662-2024</t>
+          <t>A 27403-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45442</v>
+        <v>46189</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2438,16 +2438,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.2</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2471,159 +2471,159 @@
         <v>3</v>
       </c>
       <c r="T18" t="n">
+        <v>6</v>
+      </c>
+      <c r="U18" t="n">
+        <v>6</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1489/artfynd/A 27403-2026 artfynd.xlsx", "A 27403-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1489/kartor/A 27403-2026 karta.png", "A 27403-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1489/kartor_geotiff/A 27403-2026 georefererad karta.tif", "A 27403-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1489/klagomål/A 27403-2026 FSC-klagomål.docx", "A 27403-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1489/klagomålsmail/A 27403-2026 FSC-klagomål mail.docx", "A 27403-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1489/tillsyn/A 27403-2026 tillsynsbegäran.docx", "A 27403-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1489/tillsynsmail/A 27403-2026 tillsynsbegäran mail.docx", "A 27403-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1489/fåglar/A 27403-2026 prioriterade fågelarter.docx", "A 27403-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 21662-2024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45442</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ALINGSÅS</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J19" t="n">
         <v>3</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Göktyta
 Törnskata
 Ärtsångare</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1489/artfynd/A 21662-2024 artfynd.xlsx", "A 21662-2024")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1489/kartor/A 21662-2024 karta.png", "A 21662-2024")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1489/kartor_geotiff/A 21662-2024 georefererad karta.tif", "A 21662-2024")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1489/klagomål/A 21662-2024 FSC-klagomål.docx", "A 21662-2024")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1489/klagomålsmail/A 21662-2024 FSC-klagomål mail.docx", "A 21662-2024")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1489/tillsyn/A 21662-2024 tillsynsbegäran.docx", "A 21662-2024")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1489/tillsynsmail/A 21662-2024 tillsynsbegäran mail.docx", "A 21662-2024")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1489/fåglar/A 21662-2024 prioriterade fågelarter.docx", "A 21662-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 27403-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46189</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ALINGSÅS</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>6</v>
-      </c>
-      <c r="U19" t="n">
-        <v>6</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1489/artfynd/A 27403-2026 artfynd.xlsx", "A 27403-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1489/kartor/A 27403-2026 karta.png", "A 27403-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1489/kartor_geotiff/A 27403-2026 georefererad karta.tif", "A 27403-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1489/klagomål/A 27403-2026 FSC-klagomål.docx", "A 27403-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1489/klagomålsmail/A 27403-2026 FSC-klagomål mail.docx", "A 27403-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1489/tillsyn/A 27403-2026 tillsynsbegäran.docx", "A 27403-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1489/tillsynsmail/A 27403-2026 tillsynsbegäran mail.docx", "A 27403-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1489/fåglar/A 27403-2026 prioriterade fågelarter.docx", "A 27403-2026")</f>
         <v/>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>46275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45279</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45630</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>46044</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>46245</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45607</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45483</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>45640</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>45889</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>45271</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45812</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>45330</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>46044</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>46108</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>45607</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45541</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>45366</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>44628</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>44614</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44831</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>44754</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>44637</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>44708</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>44817</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>44516</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 47234-2022</t>
+          <t>A 31303-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5137,14 +5137,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44852</v>
+        <v>44773</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5200,7 +5200,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 31303-2022</t>
+          <t>A 47234-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5210,14 +5210,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44773</v>
+        <v>44852</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5290,7 +5290,7 @@
         <v>44809</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>44572</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>44652</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>44510</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>44515</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 60657-2021</t>
+          <t>A 70426-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5652,10 +5652,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44496</v>
+        <v>44536</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5711,7 +5711,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 70426-2021</t>
+          <t>A 60657-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44536</v>
+        <v>44496</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5801,7 +5801,7 @@
         <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 51167-2021</t>
+          <t>A 981-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5871,10 +5871,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44461</v>
+        <v>44568</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 981-2022</t>
+          <t>A 37509-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5944,10 +5944,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44568</v>
+        <v>44809</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6003,7 +6003,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 37509-2022</t>
+          <t>A 3045-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44809</v>
+        <v>44582</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6076,7 +6076,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3045-2022</t>
+          <t>A 23129-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6090,10 +6090,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44582</v>
+        <v>44719</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6149,7 +6149,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 23129-2022</t>
+          <t>A 34684-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44719</v>
+        <v>44795</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6222,7 +6222,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 34684-2022</t>
+          <t>A 12884-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6236,10 +6236,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44795</v>
+        <v>44642</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 12884-2022</t>
+          <t>A 24464-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44642</v>
+        <v>44726</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6368,7 +6368,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24464-2022</t>
+          <t>A 58410-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6382,10 +6382,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44726</v>
+        <v>45634</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>8.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6441,7 +6441,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 58410-2024</t>
+          <t>A 8980-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6455,10 +6455,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45634</v>
+        <v>44979</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.7</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6531,7 +6531,7 @@
         <v>45456</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31873-2023</t>
+          <t>A 11023-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45118</v>
+        <v>44991</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6660,7 +6660,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 11023-2023</t>
+          <t>A 58990-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6674,10 +6674,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44991</v>
+        <v>44903</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6689,8 +6689,13 @@
           <t>ALINGSÅS</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6733,7 +6738,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58990-2022</t>
+          <t>A 3172-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6747,10 +6752,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44903</v>
+        <v>44582</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6762,13 +6767,8 @@
           <t>ALINGSÅS</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3172-2022</t>
+          <t>A 50633-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6825,10 +6825,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44582</v>
+        <v>45210</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6901,7 +6901,7 @@
         <v>45660</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 50633-2023</t>
+          <t>A 25749-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6971,10 +6971,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45210</v>
+        <v>45465</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7030,7 +7030,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 25749-2024</t>
+          <t>A 59303-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45465</v>
+        <v>45637</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7103,7 +7103,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 59303-2024</t>
+          <t>A 54615-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7117,10 +7117,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45637</v>
+        <v>45617</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 54615-2024</t>
+          <t>A 15019-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7190,10 +7190,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45617</v>
+        <v>45015</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 8980-2023</t>
+          <t>A 45323-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7263,10 +7263,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44979</v>
+        <v>45576</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7339,7 +7339,7 @@
         <v>45329</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 45323-2024</t>
+          <t>A 27431-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7409,10 +7409,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45576</v>
+        <v>45097</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7468,7 +7468,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 27431-2023</t>
+          <t>A 52297-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45097</v>
+        <v>45608</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 52297-2024</t>
+          <t>A 52302-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7558,7 +7558,7 @@
         <v>45608</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7614,7 +7614,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 52302-2024</t>
+          <t>A 43435-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7628,10 +7628,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45608</v>
+        <v>45568</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7687,7 +7687,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 43435-2024</t>
+          <t>A 25746-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7701,10 +7701,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45568</v>
+        <v>45465</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7760,7 +7760,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 25746-2024</t>
+          <t>A 59566-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7774,10 +7774,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45465</v>
+        <v>45254</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7833,7 +7833,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 15019-2023</t>
+          <t>A 36291-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7847,10 +7847,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45015</v>
+        <v>45534</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7906,7 +7906,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 59566-2023</t>
+          <t>A 31873-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7920,10 +7920,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45254</v>
+        <v>45118</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7979,7 +7979,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 36291-2024</t>
+          <t>A 5808-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7993,10 +7993,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45534</v>
+        <v>45335</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8052,7 +8052,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 51169-2021</t>
+          <t>A 5810-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8066,10 +8066,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44461</v>
+        <v>45335</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8125,7 +8125,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 5808-2024</t>
+          <t>A 3352-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8139,10 +8139,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45335</v>
+        <v>45679</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8198,7 +8198,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 5810-2024</t>
+          <t>A 30478-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8212,10 +8212,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45335</v>
+        <v>45111</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8271,7 +8271,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 3352-2025</t>
+          <t>A 46240-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45679</v>
+        <v>45196</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8344,7 +8344,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 30478-2023</t>
+          <t>A 11024-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8358,10 +8358,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45111</v>
+        <v>44991</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8417,7 +8417,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 46240-2023</t>
+          <t>A 11539-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8431,10 +8431,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45196</v>
+        <v>44631</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8490,7 +8490,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 11024-2023</t>
+          <t>A 8599-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8504,10 +8504,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44991</v>
+        <v>44977</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8563,7 +8563,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 8599-2023</t>
+          <t>A 16117-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8577,10 +8577,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44977</v>
+        <v>45406</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8636,7 +8636,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 11539-2022</t>
+          <t>A 58558-2021</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8650,10 +8650,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44631</v>
+        <v>44488</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8709,7 +8709,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 16117-2024</t>
+          <t>A 4661-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8723,10 +8723,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45406</v>
+        <v>45687</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8782,7 +8782,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 58558-2021</t>
+          <t>A 8828-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8796,10 +8796,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44488</v>
+        <v>45356</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8855,7 +8855,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 4661-2025</t>
+          <t>A 60904-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8869,10 +8869,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45687</v>
+        <v>45261</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8928,7 +8928,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 8828-2024</t>
+          <t>A 3355-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8942,10 +8942,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45356</v>
+        <v>44949</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9001,7 +9001,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 60904-2023</t>
+          <t>A 63143-2021</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9015,10 +9015,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45261</v>
+        <v>44505</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9074,7 +9074,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 3355-2023</t>
+          <t>A 53628-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9088,10 +9088,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44949</v>
+        <v>45230</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 63143-2021</t>
+          <t>A 24579-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9161,10 +9161,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44505</v>
+        <v>44727</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.5</v>
+        <v>10.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9220,7 +9220,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 53628-2023</t>
+          <t>A 32286-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9230,14 +9230,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45230</v>
+        <v>45512</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9293,7 +9293,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 24579-2022</t>
+          <t>A 3769-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9307,10 +9307,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44727</v>
+        <v>45681</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>10.4</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9366,7 +9366,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 4846-2024</t>
+          <t>A 40242-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9380,10 +9380,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45329</v>
+        <v>45894</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9439,7 +9439,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 3769-2025</t>
+          <t>A 4846-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9453,10 +9453,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45681</v>
+        <v>45329</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9512,7 +9512,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 32286-2024</t>
+          <t>A 26164-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9522,14 +9522,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45512</v>
+        <v>45468</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9585,7 +9585,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 26164-2024</t>
+          <t>A 6120-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9595,14 +9595,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45468</v>
+        <v>44964</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9658,7 +9658,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 8981-2023</t>
+          <t>A 23617-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44979</v>
+        <v>45792</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9731,7 +9731,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 57491-2022</t>
+          <t>A 8981-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9745,10 +9745,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44896</v>
+        <v>44979</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9804,7 +9804,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 23617-2025</t>
+          <t>A 57491-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45792</v>
+        <v>44896</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 6120-2023</t>
+          <t>A 40073-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9887,14 +9887,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44964</v>
+        <v>45894</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9950,7 +9950,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 51178-2023</t>
+          <t>A 41454-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9964,10 +9964,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45219</v>
+        <v>45901</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10023,7 +10023,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 25744-2024</t>
+          <t>A 44103-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10037,10 +10037,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45465</v>
+        <v>45915</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>6.1</v>
+        <v>2.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10096,7 +10096,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 25748-2024</t>
+          <t>A 42490-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10110,10 +10110,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45465</v>
+        <v>45905</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10169,7 +10169,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 44103-2025</t>
+          <t>A 21328-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10183,10 +10183,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45915</v>
+        <v>45782</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10242,7 +10242,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 40242-2025</t>
+          <t>A 42672-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10256,10 +10256,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45894</v>
+        <v>45908</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10315,7 +10315,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 57489-2022</t>
+          <t>A 42710-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10325,14 +10325,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44896</v>
+        <v>45908</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>10</v>
+        <v>1.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10388,7 +10388,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 29837-2025</t>
+          <t>A 42711-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10398,14 +10398,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45826</v>
+        <v>45908</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10461,7 +10461,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 21328-2025</t>
+          <t>A 43262-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10475,10 +10475,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45782</v>
+        <v>45910</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10534,7 +10534,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 40073-2025</t>
+          <t>A 29837-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10548,10 +10548,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45894</v>
+        <v>45826</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10624,7 +10624,7 @@
         <v>45772</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 41454-2025</t>
+          <t>A 3618-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10694,10 +10694,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45901</v>
+        <v>45681</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10753,7 +10753,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 41452-2025</t>
+          <t>A 44530-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10767,10 +10767,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45901</v>
+        <v>45916</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10826,7 +10826,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 3618-2025</t>
+          <t>A 51178-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10840,10 +10840,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45681</v>
+        <v>45219</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10899,7 +10899,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 42490-2025</t>
+          <t>A 25744-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45905</v>
+        <v>45465</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.8</v>
+        <v>6.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10972,7 +10972,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 33812-2023</t>
+          <t>A 25748-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10986,10 +10986,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45133</v>
+        <v>45465</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11045,7 +11045,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 42672-2025</t>
+          <t>A 45610-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11059,10 +11059,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45908</v>
+        <v>45922</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11118,7 +11118,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 42710-2025</t>
+          <t>A 47143-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11128,14 +11128,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45908</v>
+        <v>45929</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11191,7 +11191,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 42711-2025</t>
+          <t>A 57489-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11201,14 +11201,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45908</v>
+        <v>44896</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.8</v>
+        <v>10</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11264,7 +11264,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 43262-2025</t>
+          <t>A 47562-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45910</v>
+        <v>45931</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11337,7 +11337,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 9711-2023</t>
+          <t>A 64194-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11347,14 +11347,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44984</v>
+        <v>45279</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11366,8 +11366,13 @@
           <t>ALINGSÅS</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11410,7 +11415,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 8080-2023</t>
+          <t>A 16609-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11424,10 +11429,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44974</v>
+        <v>44672</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11440,7 +11445,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11483,7 +11488,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 33490-2025</t>
+          <t>A 16612-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11493,14 +11498,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45841</v>
+        <v>44672</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11513,7 +11518,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>7.9</v>
+        <v>0.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11556,7 +11561,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 44530-2025</t>
+          <t>A 64070-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11566,14 +11571,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45916</v>
+        <v>45279</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11585,8 +11590,13 @@
           <t>ALINGSÅS</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11629,7 +11639,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 5757-2022</t>
+          <t>A 64058-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11643,10 +11653,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44596</v>
+        <v>45279</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11658,8 +11668,13 @@
           <t>ALINGSÅS</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11702,7 +11717,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 45610-2025</t>
+          <t>A 33490-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11716,10 +11731,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45922</v>
+        <v>45841</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11732,7 +11747,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.8</v>
+        <v>7.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11775,7 +11790,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 56752-2023</t>
+          <t>A 48942-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11789,10 +11804,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45244</v>
+        <v>45937</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11805,7 +11820,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11848,7 +11863,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 50312-2024</t>
+          <t>A 48966-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11862,10 +11877,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45600</v>
+        <v>45937</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11878,7 +11893,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11921,7 +11936,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 47143-2025</t>
+          <t>A 49420-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11935,10 +11950,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45929</v>
+        <v>45938</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11951,7 +11966,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11994,7 +12009,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 47562-2025</t>
+          <t>A 33812-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12008,10 +12023,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45931</v>
+        <v>45133</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12024,7 +12039,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12067,7 +12082,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 64194-2023</t>
+          <t>A 10916-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12077,14 +12092,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45279</v>
+        <v>45722</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12096,13 +12111,8 @@
           <t>ALINGSÅS</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12145,7 +12155,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 16609-2022</t>
+          <t>A 9711-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12159,10 +12169,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44672</v>
+        <v>44984</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12175,7 +12185,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12218,7 +12228,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 16612-2022</t>
+          <t>A 8080-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12228,14 +12238,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44672</v>
+        <v>44974</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12248,7 +12258,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.6</v>
+        <v>5.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12291,7 +12301,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 64070-2023</t>
+          <t>A 45612-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12301,14 +12311,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45279</v>
+        <v>45922</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12320,13 +12330,8 @@
           <t>ALINGSÅS</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12369,7 +12374,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 64058-2023</t>
+          <t>A 5757-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12383,10 +12388,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45279</v>
+        <v>44596</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12398,13 +12403,8 @@
           <t>ALINGSÅS</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12447,7 +12447,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 59925-2023</t>
+          <t>A 56752-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12461,10 +12461,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45257</v>
+        <v>45244</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 48942-2025</t>
+          <t>A 53222-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12534,10 +12534,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45937</v>
+        <v>45958</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>8.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12593,7 +12593,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 48966-2025</t>
+          <t>A 53223-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12607,10 +12607,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45937</v>
+        <v>45958</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12623,7 +12623,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12666,7 +12666,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 49420-2025</t>
+          <t>A 49522-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12680,10 +12680,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45938</v>
+        <v>45596</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12739,7 +12739,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 9181-2022</t>
+          <t>A 50312-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12753,10 +12753,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44615</v>
+        <v>45600</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>5.5</v>
+        <v>0.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12812,7 +12812,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 42865-2022</t>
+          <t>A 54122-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44832</v>
+        <v>45964</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12885,7 +12885,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 10916-2025</t>
+          <t>A 54073-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12895,14 +12895,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45722</v>
+        <v>45964</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12958,7 +12958,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 25141-2022</t>
+          <t>A 54074-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12972,10 +12972,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44729</v>
+        <v>45964</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13031,7 +13031,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 45612-2025</t>
+          <t>A 54644-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13041,14 +13041,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45922</v>
+        <v>45966</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13104,7 +13104,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 11119-2024</t>
+          <t>A 54643-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13118,10 +13118,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45371</v>
+        <v>45966</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13177,7 +13177,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 18940-2024</t>
+          <t>A 55294-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13187,14 +13187,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45427</v>
+        <v>45969</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13250,7 +13250,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 17048-2024</t>
+          <t>A 55775-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13264,10 +13264,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45412</v>
+        <v>45972</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 2362-2024</t>
+          <t>A 59925-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13333,14 +13333,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45310</v>
+        <v>45257</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13396,7 +13396,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 53222-2025</t>
+          <t>A 57912-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13410,10 +13410,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45958</v>
+        <v>45972</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13469,7 +13469,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 53223-2025</t>
+          <t>A 56311-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13483,10 +13483,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45958</v>
+        <v>45974</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13542,7 +13542,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 54122-2025</t>
+          <t>A 56118-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13556,10 +13556,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45964</v>
+        <v>45973</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13615,7 +13615,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 54073-2025</t>
+          <t>A 56116-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13629,10 +13629,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45964</v>
+        <v>45973</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13688,7 +13688,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 54074-2025</t>
+          <t>A 9181-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13702,10 +13702,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45964</v>
+        <v>44615</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.7</v>
+        <v>5.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13761,7 +13761,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 40293-2022</t>
+          <t>A 42865-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13775,10 +13775,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44821</v>
+        <v>44832</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13834,7 +13834,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 53887-2021</t>
+          <t>A 25141-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13848,10 +13848,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44469</v>
+        <v>44729</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13864,7 +13864,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.6</v>
+        <v>7.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13907,7 +13907,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 54644-2025</t>
+          <t>A 11119-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13917,14 +13917,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45966</v>
+        <v>45371</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13980,7 +13980,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 54643-2025</t>
+          <t>A 18940-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13994,10 +13994,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45966</v>
+        <v>45427</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14053,7 +14053,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 18159-2024</t>
+          <t>A 58636-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14067,10 +14067,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45420</v>
+        <v>45986</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14126,7 +14126,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 55294-2025</t>
+          <t>A 22186-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14140,10 +14140,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45969</v>
+        <v>45785</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14199,7 +14199,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 55775-2025</t>
+          <t>A 59396-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14213,10 +14213,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45972</v>
+        <v>45989</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14228,8 +14228,13 @@
           <t>ALINGSÅS</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14272,7 +14277,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 12600-2024</t>
+          <t>A 59397-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14286,10 +14291,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45380</v>
+        <v>45989</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14301,8 +14306,13 @@
           <t>ALINGSÅS</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14345,7 +14355,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 57912-2025</t>
+          <t>A 17048-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14359,10 +14369,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45972</v>
+        <v>45412</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14375,7 +14385,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14418,7 +14428,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 56311-2025</t>
+          <t>A 24995-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14432,10 +14442,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45974</v>
+        <v>46174</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14448,7 +14458,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14491,7 +14501,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 56118-2025</t>
+          <t>A 24845-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14505,10 +14515,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45973</v>
+        <v>46174</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14521,7 +14531,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14564,7 +14574,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 56116-2025</t>
+          <t>A 2362-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14574,14 +14584,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45973</v>
+        <v>45310</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14594,7 +14604,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14637,7 +14647,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 24607-2022</t>
+          <t>A 24668-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14651,10 +14661,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44727</v>
+        <v>46171</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14667,7 +14677,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>9.5</v>
+        <v>0.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14710,7 +14720,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 59956-2023</t>
+          <t>A 24847-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14724,10 +14734,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45257</v>
+        <v>46174</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14740,7 +14750,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14783,7 +14793,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 58636-2025</t>
+          <t>A 60725-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14797,10 +14807,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45986</v>
+        <v>45996</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14813,7 +14823,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.3</v>
+        <v>5.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14856,7 +14866,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 22186-2025</t>
+          <t>A 61205-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14866,14 +14876,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45785</v>
+        <v>46000</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14886,7 +14896,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14929,7 +14939,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 59396-2025</t>
+          <t>A 61134-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14943,10 +14953,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45989</v>
+        <v>46000</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14958,13 +14968,8 @@
           <t>ALINGSÅS</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15007,7 +15012,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 59397-2025</t>
+          <t>A 40293-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15021,10 +15026,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45989</v>
+        <v>44821</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15036,13 +15041,8 @@
           <t>ALINGSÅS</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15085,7 +15085,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 23559-2022</t>
+          <t>A 53887-2021</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15099,10 +15099,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44721</v>
+        <v>44469</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15158,7 +15158,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 61734-2023</t>
+          <t>A 25302-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15172,10 +15172,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45265</v>
+        <v>46176</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15231,7 +15231,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 49522-2024</t>
+          <t>A 18159-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15245,10 +15245,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45596</v>
+        <v>45420</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>8.300000000000001</v>
+        <v>1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15304,7 +15304,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 15006-2024</t>
+          <t>A 25457-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15318,10 +15318,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45399</v>
+        <v>46177</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15377,7 +15377,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 60725-2025</t>
+          <t>A 62818-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15391,10 +15391,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45996</v>
+        <v>46008</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15450,7 +15450,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 61205-2025</t>
+          <t>A 12600-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15464,10 +15464,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46000</v>
+        <v>45380</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15523,7 +15523,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 61134-2025</t>
+          <t>A 25462-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15537,10 +15537,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46000</v>
+        <v>46177</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15596,7 +15596,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 48082-2024</t>
+          <t>A 25468-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15610,10 +15610,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45589</v>
+        <v>46177</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15669,7 +15669,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 42531-2022</t>
+          <t>A 25469-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15683,10 +15683,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44831</v>
+        <v>46177</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15742,7 +15742,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 21727-2022</t>
+          <t>A 25775-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15756,10 +15756,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44708</v>
+        <v>46178</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15815,7 +15815,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 23181-2023</t>
+          <t>A 63716-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15829,10 +15829,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45075</v>
+        <v>46014</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>13.1</v>
+        <v>7.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15888,7 +15888,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 62818-2025</t>
+          <t>A 63717-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15902,10 +15902,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15961,7 +15961,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 4806-2023</t>
+          <t>A 8210-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15975,10 +15975,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44957</v>
+        <v>45708</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16034,7 +16034,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 52298-2024</t>
+          <t>A 8234-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16048,10 +16048,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45608</v>
+        <v>45708</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16107,7 +16107,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 63716-2025</t>
+          <t>A 6341-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16121,10 +16121,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46014</v>
+        <v>45699</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>7.5</v>
+        <v>1.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16180,7 +16180,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 63717-2025</t>
+          <t>A 24607-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16194,10 +16194,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46014</v>
+        <v>44727</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>3.3</v>
+        <v>9.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16253,7 +16253,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 8210-2025</t>
+          <t>A 1837-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16267,10 +16267,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45708</v>
+        <v>46035</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16326,7 +16326,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 8234-2025</t>
+          <t>A 59956-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16340,10 +16340,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45708</v>
+        <v>45257</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16399,7 +16399,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 6341-2025</t>
+          <t>A 23559-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16413,10 +16413,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45699</v>
+        <v>44721</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16472,7 +16472,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 15798-2023</t>
+          <t>A 3049-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16486,10 +16486,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45021</v>
+        <v>46038</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16545,7 +16545,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 62678-2023</t>
+          <t>A 3048-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16559,10 +16559,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45271</v>
+        <v>46038</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16618,7 +16618,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 47233-2022</t>
+          <t>A 3008-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16632,10 +16632,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44852</v>
+        <v>46038</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16691,7 +16691,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 39472-2023</t>
+          <t>A 3028-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16705,10 +16705,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45166</v>
+        <v>46038</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16764,7 +16764,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 1837-2026</t>
+          <t>A 61734-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16778,10 +16778,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46035</v>
+        <v>45265</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16837,7 +16837,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 24995-2026</t>
+          <t>A 27029-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16851,10 +16851,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46174</v>
+        <v>46185</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16910,7 +16910,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 24845-2026</t>
+          <t>A 4203-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16924,10 +16924,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46174</v>
+        <v>46044</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16983,7 +16983,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 24668-2026</t>
+          <t>A 27404-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16997,10 +16997,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46171</v>
+        <v>46189</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17056,7 +17056,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 3049-2026</t>
+          <t>A 27401-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17070,10 +17070,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46038</v>
+        <v>46189</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17129,7 +17129,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 5962-2023</t>
+          <t>A 27882-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17143,10 +17143,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44964</v>
+        <v>46191</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17202,7 +17202,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 3048-2026</t>
+          <t>A 15006-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17216,10 +17216,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46038</v>
+        <v>45399</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17275,7 +17275,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 3008-2026</t>
+          <t>A 27877-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17289,10 +17289,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46038</v>
+        <v>46191</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17348,7 +17348,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 13858-2024</t>
+          <t>A 48082-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17362,10 +17362,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45391</v>
+        <v>45589</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17421,7 +17421,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 3028-2026</t>
+          <t>A 42531-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17435,10 +17435,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46038</v>
+        <v>44831</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17451,7 +17451,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17494,7 +17494,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 24847-2026</t>
+          <t>A 21727-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17508,10 +17508,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46174</v>
+        <v>44708</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17524,7 +17524,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17567,7 +17567,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 36332-2023</t>
+          <t>A 23181-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17581,10 +17581,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45152</v>
+        <v>45075</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17597,7 +17597,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>3.6</v>
+        <v>13.1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 4203-2026</t>
+          <t>A 9362-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17654,10 +17654,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46044</v>
+        <v>46070</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17713,7 +17713,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 25343-2026</t>
+          <t>A 4806-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17723,14 +17723,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46176</v>
+        <v>44957</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 25302-2026</t>
+          <t>A 52298-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17800,10 +17800,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46176</v>
+        <v>45608</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17859,7 +17859,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 25313-2026</t>
+          <t>A 12168-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17873,10 +17873,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46176</v>
+        <v>46086</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17932,7 +17932,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 25457-2026</t>
+          <t>A 15798-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17946,10 +17946,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46177</v>
+        <v>45021</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18005,7 +18005,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 4147-2023</t>
+          <t>A 62678-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18019,10 +18019,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44953</v>
+        <v>45271</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18078,7 +18078,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 25462-2026</t>
+          <t>A 12039-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18092,10 +18092,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46177</v>
+        <v>46086</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18151,7 +18151,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 25468-2026</t>
+          <t>A 47233-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18165,10 +18165,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46177</v>
+        <v>44852</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18181,7 +18181,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18224,7 +18224,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 25469-2026</t>
+          <t>A 39472-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18238,10 +18238,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46177</v>
+        <v>45166</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18297,7 +18297,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 25775-2026</t>
+          <t>A 5962-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18311,10 +18311,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46178</v>
+        <v>44964</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18370,7 +18370,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 9362-2026</t>
+          <t>A 13858-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18384,10 +18384,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46070</v>
+        <v>45391</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18443,7 +18443,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 43741-2024</t>
+          <t>A 36332-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18457,10 +18457,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45569</v>
+        <v>45152</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18516,7 +18516,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 12322-2024</t>
+          <t>A 15988-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18530,10 +18530,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45378</v>
+        <v>46108</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18546,7 +18546,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18589,7 +18589,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 47960-2022</t>
+          <t>A 16077-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18603,10 +18603,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44855</v>
+        <v>46108</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18662,7 +18662,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 12168-2026</t>
+          <t>A 16086-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18676,10 +18676,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46086</v>
+        <v>46108</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18735,7 +18735,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 12039-2026</t>
+          <t>A 33222-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18749,10 +18749,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46086</v>
+        <v>46246</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18808,7 +18808,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 27029-2026</t>
+          <t>A 33571-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18822,10 +18822,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46185</v>
+        <v>46248</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18838,7 +18838,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18881,7 +18881,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 27404-2026</t>
+          <t>A 33574-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18895,10 +18895,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46189</v>
+        <v>46248</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18954,7 +18954,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 27401-2026</t>
+          <t>A 4147-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18968,10 +18968,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46189</v>
+        <v>44953</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -19027,7 +19027,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 7713-2024</t>
+          <t>A 17834-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19041,10 +19041,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45349</v>
+        <v>46122</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19100,7 +19100,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 26316-2023</t>
+          <t>A 17680-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19114,10 +19114,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45091</v>
+        <v>46121</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>5.6</v>
+        <v>1.6</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19173,7 +19173,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 27882-2026</t>
+          <t>A 17654-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19187,10 +19187,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46191</v>
+        <v>46121</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19246,7 +19246,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 27877-2026</t>
+          <t>A 18360-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19256,14 +19256,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46191</v>
+        <v>46126</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19275,8 +19275,13 @@
           <t>ALINGSÅS</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I239" t="n">
-        <v>21</v>
+        <v>0.4</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19319,7 +19324,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 38508-2024</t>
+          <t>A 18889-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19333,10 +19338,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45546</v>
+        <v>46129</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19349,7 +19354,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19392,7 +19397,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 15846-2026</t>
+          <t>A 18574-2026</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19406,10 +19411,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>46107</v>
+        <v>46127</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19422,7 +19427,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19465,7 +19470,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 15988-2026</t>
+          <t>A 19025-2026</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19479,10 +19484,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46108</v>
+        <v>46131</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19495,7 +19500,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19538,7 +19543,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 16077-2026</t>
+          <t>A 43741-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19552,10 +19557,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>46108</v>
+        <v>45569</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19568,7 +19573,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19611,7 +19616,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 15847-2026</t>
+          <t>A 12322-2024</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19625,10 +19630,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46107</v>
+        <v>45378</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19641,7 +19646,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19684,7 +19689,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 45322-2024</t>
+          <t>A 47960-2022</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19698,10 +19703,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45576</v>
+        <v>44855</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19714,7 +19719,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19757,7 +19762,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 16086-2026</t>
+          <t>A 34543-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19771,10 +19776,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46108</v>
+        <v>46255</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19787,7 +19792,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19830,7 +19835,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 14313-2023</t>
+          <t>A 7713-2024</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19844,10 +19849,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45011</v>
+        <v>45349</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19860,7 +19865,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19903,7 +19908,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 59541-2022</t>
+          <t>A 26316-2023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19917,10 +19922,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>44907</v>
+        <v>45091</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19933,7 +19938,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19976,7 +19981,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 33089-2026</t>
+          <t>A 38508-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19990,10 +19995,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>46245</v>
+        <v>45546</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20006,7 +20011,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -20049,7 +20054,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 33151-2026</t>
+          <t>A 45322-2024</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -20063,10 +20068,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>46245</v>
+        <v>45576</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20079,7 +20084,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -20122,7 +20127,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 12318-2022</t>
+          <t>A 14313-2023</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20136,10 +20141,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>44637</v>
+        <v>45011</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20152,7 +20157,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20195,7 +20200,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 52299-2024</t>
+          <t>A 59541-2022</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20209,10 +20214,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45608</v>
+        <v>44907</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20225,7 +20230,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20268,7 +20273,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 17834-2026</t>
+          <t>A 12318-2022</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20282,10 +20287,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>46122</v>
+        <v>44637</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20298,7 +20303,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20341,7 +20346,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 17680-2026</t>
+          <t>A 52299-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20355,10 +20360,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>46121</v>
+        <v>45608</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20371,7 +20376,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20414,7 +20419,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 17654-2026</t>
+          <t>A 35529-2026</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20428,10 +20433,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>46121</v>
+        <v>46262</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20444,7 +20449,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20487,7 +20492,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 18360-2026</t>
+          <t>A 37429-2023</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20497,14 +20502,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>46126</v>
+        <v>45156</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20518,11 +20523,11 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I256" t="n">
-        <v>0.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20565,7 +20570,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 18889-2026</t>
+          <t>A 25747-2024</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20579,10 +20584,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>46129</v>
+        <v>45465</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20595,7 +20600,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20638,7 +20643,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 37429-2023</t>
+          <t>A 36000-2026</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20652,10 +20657,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45156</v>
+        <v>46266</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20667,13 +20672,8 @@
           <t>ALINGSÅS</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I258" t="n">
-        <v>9.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20716,7 +20716,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 18574-2026</t>
+          <t>A 57450-2024</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20730,10 +20730,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>46127</v>
+        <v>45630</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20789,7 +20789,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 25747-2024</t>
+          <t>A 3495-2023</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20803,10 +20803,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45465</v>
+        <v>44949</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20862,7 +20862,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 19025-2026</t>
+          <t>A 21143-2024</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20876,10 +20876,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>46131</v>
+        <v>45440</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20935,7 +20935,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 57450-2024</t>
+          <t>A 62671-2023</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20949,10 +20949,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45630</v>
+        <v>45271</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20965,7 +20965,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -21008,7 +21008,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 3495-2023</t>
+          <t>A 15018-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -21022,10 +21022,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>44949</v>
+        <v>45015</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -21081,7 +21081,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 21143-2024</t>
+          <t>A 8620-2023</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -21095,10 +21095,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45440</v>
+        <v>44977</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -21154,7 +21154,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 62671-2023</t>
+          <t>A 60027-2023</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21168,10 +21168,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45271</v>
+        <v>45258</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -21227,7 +21227,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 15018-2023</t>
+          <t>A 39471-2023</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21241,10 +21241,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45015</v>
+        <v>45166</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -21300,7 +21300,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 8620-2023</t>
+          <t>A 38955-2022</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21314,10 +21314,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>44977</v>
+        <v>44816</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21373,7 +21373,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 60027-2023</t>
+          <t>A 31970-2026</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21387,10 +21387,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45258</v>
+        <v>46232</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21403,7 +21403,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21446,7 +21446,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 39471-2023</t>
+          <t>A 40880-2023</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21460,10 +21460,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45166</v>
+        <v>45173</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21476,7 +21476,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21519,7 +21519,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 33222-2026</t>
+          <t>A 38292-2026</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21533,10 +21533,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>46246</v>
+        <v>46282</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21592,7 +21592,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 33571-2026</t>
+          <t>A 7805-2025</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21606,10 +21606,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>46248</v>
+        <v>45706</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21665,7 +21665,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 33574-2026</t>
+          <t>A 25743-2024</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21679,10 +21679,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>46248</v>
+        <v>45465</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21738,7 +21738,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 38955-2022</t>
+          <t>A 33151-2026</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21752,10 +21752,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>44816</v>
+        <v>46245</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21811,7 +21811,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 40880-2023</t>
+          <t>A 19562-2024</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21825,10 +21825,10 @@
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>45173</v>
+        <v>45429</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21884,7 +21884,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A 34543-2026</t>
+          <t>A 33089-2026</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21898,10 +21898,10 @@
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>46255</v>
+        <v>46245</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -21957,7 +21957,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>A 7805-2025</t>
+          <t>A 41971-2023</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -21971,10 +21971,10 @@
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>45706</v>
+        <v>45177</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -22030,7 +22030,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>A 25743-2024</t>
+          <t>A 49164-2024</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -22044,10 +22044,10 @@
         </is>
       </c>
       <c r="D277" s="1" t="n">
-        <v>45465</v>
+        <v>45594</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -22103,7 +22103,7 @@
     <row r="278" ht="15" customHeight="1">
       <c r="A278" t="inlineStr">
         <is>
-          <t>A 19562-2024</t>
+          <t>A 10587-2025</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -22117,10 +22117,10 @@
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>45429</v>
+        <v>45721</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -22176,7 +22176,7 @@
     <row r="279" ht="15" customHeight="1">
       <c r="A279" t="inlineStr">
         <is>
-          <t>A 35529-2026</t>
+          <t>A 33491-2024</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -22190,10 +22190,10 @@
         </is>
       </c>
       <c r="D279" s="1" t="n">
-        <v>46262</v>
+        <v>45519</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22206,7 +22206,7 @@
         </is>
       </c>
       <c r="I279" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
@@ -22249,7 +22249,7 @@
     <row r="280" ht="15" customHeight="1">
       <c r="A280" t="inlineStr">
         <is>
-          <t>A 41971-2023</t>
+          <t>A 23533-2025</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -22263,10 +22263,10 @@
         </is>
       </c>
       <c r="D280" s="1" t="n">
-        <v>45177</v>
+        <v>45792</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         </is>
       </c>
       <c r="I280" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J280" t="n">
         <v>0</v>
@@ -22322,7 +22322,7 @@
     <row r="281" ht="15" customHeight="1">
       <c r="A281" t="inlineStr">
         <is>
-          <t>A 49164-2024</t>
+          <t>A 3748-2025</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -22336,10 +22336,10 @@
         </is>
       </c>
       <c r="D281" s="1" t="n">
-        <v>45594</v>
+        <v>45681</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         </is>
       </c>
       <c r="I281" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -22395,7 +22395,7 @@
     <row r="282" ht="15" customHeight="1">
       <c r="A282" t="inlineStr">
         <is>
-          <t>A 36000-2026</t>
+          <t>A 32026-2024</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -22409,10 +22409,10 @@
         </is>
       </c>
       <c r="D282" s="1" t="n">
-        <v>46266</v>
+        <v>45510</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         </is>
       </c>
       <c r="I282" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
@@ -22468,7 +22468,7 @@
     <row r="283" ht="15" customHeight="1">
       <c r="A283" t="inlineStr">
         <is>
-          <t>A 10587-2025</t>
+          <t>A 60026-2023</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -22482,10 +22482,10 @@
         </is>
       </c>
       <c r="D283" s="1" t="n">
-        <v>45721</v>
+        <v>45258</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         </is>
       </c>
       <c r="I283" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
@@ -22541,7 +22541,7 @@
     <row r="284" ht="15" customHeight="1">
       <c r="A284" t="inlineStr">
         <is>
-          <t>A 31970-2026</t>
+          <t>A 25562-2025</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -22555,10 +22555,10 @@
         </is>
       </c>
       <c r="D284" s="1" t="n">
-        <v>46232</v>
+        <v>45803</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
         </is>
       </c>
       <c r="I284" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J284" t="n">
         <v>0</v>
@@ -22614,7 +22614,7 @@
     <row r="285" ht="15" customHeight="1">
       <c r="A285" t="inlineStr">
         <is>
-          <t>A 33491-2024</t>
+          <t>A 26096-2025</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -22628,10 +22628,10 @@
         </is>
       </c>
       <c r="D285" s="1" t="n">
-        <v>45519</v>
+        <v>45805</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="I285" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J285" t="n">
         <v>0</v>
@@ -22687,7 +22687,7 @@
     <row r="286" ht="15" customHeight="1">
       <c r="A286" t="inlineStr">
         <is>
-          <t>A 23533-2025</t>
+          <t>A 25896-2025</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -22701,10 +22701,10 @@
         </is>
       </c>
       <c r="D286" s="1" t="n">
-        <v>45792</v>
+        <v>45804</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
     <row r="287" ht="15" customHeight="1">
       <c r="A287" t="inlineStr">
         <is>
-          <t>A 38292-2026</t>
+          <t>A 25897-2025</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -22774,10 +22774,10 @@
         </is>
       </c>
       <c r="D287" s="1" t="n">
-        <v>46282</v>
+        <v>45804</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         </is>
       </c>
       <c r="I287" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J287" t="n">
         <v>0</v>
@@ -22833,7 +22833,7 @@
     <row r="288" ht="15" customHeight="1">
       <c r="A288" t="inlineStr">
         <is>
-          <t>A 3748-2025</t>
+          <t>A 54579-2024</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -22843,14 +22843,14 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D288" s="1" t="n">
-        <v>45681</v>
+        <v>45617</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         </is>
       </c>
       <c r="I288" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J288" t="n">
         <v>0</v>
@@ -22906,7 +22906,7 @@
     <row r="289" ht="15" customHeight="1">
       <c r="A289" t="inlineStr">
         <is>
-          <t>A 32026-2024</t>
+          <t>A 12968-2025</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -22920,10 +22920,10 @@
         </is>
       </c>
       <c r="D289" s="1" t="n">
-        <v>45510</v>
+        <v>45734</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         </is>
       </c>
       <c r="I289" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J289" t="n">
         <v>0</v>
@@ -22979,7 +22979,7 @@
     <row r="290" ht="15" customHeight="1">
       <c r="A290" t="inlineStr">
         <is>
-          <t>A 60026-2023</t>
+          <t>A 12276-2024</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -22993,10 +22993,10 @@
         </is>
       </c>
       <c r="D290" s="1" t="n">
-        <v>45258</v>
+        <v>45378</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         </is>
       </c>
       <c r="I290" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J290" t="n">
         <v>0</v>
@@ -23052,7 +23052,7 @@
     <row r="291" ht="15" customHeight="1">
       <c r="A291" t="inlineStr">
         <is>
-          <t>A 25562-2025</t>
+          <t>A 27202-2025</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -23066,10 +23066,10 @@
         </is>
       </c>
       <c r="D291" s="1" t="n">
-        <v>45803</v>
+        <v>45812</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         </is>
       </c>
       <c r="I291" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J291" t="n">
         <v>0</v>
@@ -23125,7 +23125,7 @@
     <row r="292" ht="15" customHeight="1">
       <c r="A292" t="inlineStr">
         <is>
-          <t>A 26096-2025</t>
+          <t>A 28168-2025</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -23139,10 +23139,10 @@
         </is>
       </c>
       <c r="D292" s="1" t="n">
-        <v>45805</v>
+        <v>45818</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         </is>
       </c>
       <c r="I292" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J292" t="n">
         <v>0</v>
@@ -23198,7 +23198,7 @@
     <row r="293" ht="15" customHeight="1">
       <c r="A293" t="inlineStr">
         <is>
-          <t>A 25896-2025</t>
+          <t>A 10541-2025</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -23212,10 +23212,10 @@
         </is>
       </c>
       <c r="D293" s="1" t="n">
-        <v>45804</v>
+        <v>45721</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23227,8 +23227,13 @@
           <t>ALINGSÅS</t>
         </is>
       </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I293" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J293" t="n">
         <v>0</v>
@@ -23271,7 +23276,7 @@
     <row r="294" ht="15" customHeight="1">
       <c r="A294" t="inlineStr">
         <is>
-          <t>A 25897-2025</t>
+          <t>A 11388-2025</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -23285,10 +23290,10 @@
         </is>
       </c>
       <c r="D294" s="1" t="n">
-        <v>45804</v>
+        <v>45726</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23301,7 +23306,7 @@
         </is>
       </c>
       <c r="I294" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J294" t="n">
         <v>0</v>
@@ -23344,7 +23349,7 @@
     <row r="295" ht="15" customHeight="1">
       <c r="A295" t="inlineStr">
         <is>
-          <t>A 54579-2024</t>
+          <t>A 11462-2025</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -23354,14 +23359,14 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D295" s="1" t="n">
-        <v>45617</v>
+        <v>45726</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23374,7 +23379,7 @@
         </is>
       </c>
       <c r="I295" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J295" t="n">
         <v>0</v>
@@ -23417,7 +23422,7 @@
     <row r="296" ht="15" customHeight="1">
       <c r="A296" t="inlineStr">
         <is>
-          <t>A 12968-2025</t>
+          <t>A 11458-2025</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -23431,10 +23436,10 @@
         </is>
       </c>
       <c r="D296" s="1" t="n">
-        <v>45734</v>
+        <v>45726</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23447,7 +23452,7 @@
         </is>
       </c>
       <c r="I296" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J296" t="n">
         <v>0</v>
@@ -23490,7 +23495,7 @@
     <row r="297" ht="15" customHeight="1">
       <c r="A297" t="inlineStr">
         <is>
-          <t>A 12276-2024</t>
+          <t>A 11459-2025</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -23504,10 +23509,10 @@
         </is>
       </c>
       <c r="D297" s="1" t="n">
-        <v>45378</v>
+        <v>45726</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23520,7 +23525,7 @@
         </is>
       </c>
       <c r="I297" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J297" t="n">
         <v>0</v>
@@ -23563,7 +23568,7 @@
     <row r="298" ht="15" customHeight="1">
       <c r="A298" t="inlineStr">
         <is>
-          <t>A 27202-2025</t>
+          <t>A 9851-2025</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -23577,10 +23582,10 @@
         </is>
       </c>
       <c r="D298" s="1" t="n">
-        <v>45812</v>
+        <v>45716</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23593,7 +23598,7 @@
         </is>
       </c>
       <c r="I298" t="n">
-        <v>1.7</v>
+        <v>6.6</v>
       </c>
       <c r="J298" t="n">
         <v>0</v>
@@ -23636,7 +23641,7 @@
     <row r="299" ht="15" customHeight="1">
       <c r="A299" t="inlineStr">
         <is>
-          <t>A 28168-2025</t>
+          <t>A 19553-2024</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -23646,14 +23651,14 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D299" s="1" t="n">
-        <v>45818</v>
+        <v>45429</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23666,7 +23671,7 @@
         </is>
       </c>
       <c r="I299" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J299" t="n">
         <v>0</v>
@@ -23709,7 +23714,7 @@
     <row r="300" ht="15" customHeight="1">
       <c r="A300" t="inlineStr">
         <is>
-          <t>A 10541-2025</t>
+          <t>A 35003-2025</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -23723,10 +23728,10 @@
         </is>
       </c>
       <c r="D300" s="1" t="n">
-        <v>45721</v>
+        <v>45850</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23738,13 +23743,8 @@
           <t>ALINGSÅS</t>
         </is>
       </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I300" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J300" t="n">
         <v>0</v>
@@ -23787,7 +23787,7 @@
     <row r="301" ht="15" customHeight="1">
       <c r="A301" t="inlineStr">
         <is>
-          <t>A 11388-2025</t>
+          <t>A 59292-2023</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -23801,10 +23801,10 @@
         </is>
       </c>
       <c r="D301" s="1" t="n">
-        <v>45726</v>
+        <v>45253</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         </is>
       </c>
       <c r="I301" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J301" t="n">
         <v>0</v>
@@ -23860,7 +23860,7 @@
     <row r="302" ht="15" customHeight="1">
       <c r="A302" t="inlineStr">
         <is>
-          <t>A 11462-2025</t>
+          <t>A 35004-2025</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -23874,10 +23874,10 @@
         </is>
       </c>
       <c r="D302" s="1" t="n">
-        <v>45726</v>
+        <v>45850</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         </is>
       </c>
       <c r="I302" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J302" t="n">
         <v>0</v>
@@ -23933,7 +23933,7 @@
     <row r="303" ht="15" customHeight="1">
       <c r="A303" t="inlineStr">
         <is>
-          <t>A 11458-2025</t>
+          <t>A 17550-2025</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -23947,10 +23947,10 @@
         </is>
       </c>
       <c r="D303" s="1" t="n">
-        <v>45726</v>
+        <v>45757</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         </is>
       </c>
       <c r="I303" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J303" t="n">
         <v>0</v>
@@ -24006,24 +24006,24 @@
     <row r="304" ht="15" customHeight="1">
       <c r="A304" t="inlineStr">
         <is>
-          <t>A 11459-2025</t>
+          <t>S 277-2024</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D304" s="1" t="n">
-        <v>45726</v>
+        <v>45323</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         </is>
       </c>
       <c r="I304" t="n">
-        <v>1.9</v>
+        <v>60.2</v>
       </c>
       <c r="J304" t="n">
         <v>0</v>
@@ -24079,24 +24079,24 @@
     <row r="305" ht="15" customHeight="1">
       <c r="A305" t="inlineStr">
         <is>
-          <t>A 9851-2025</t>
+          <t>S 276-2024</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D305" s="1" t="n">
-        <v>45716</v>
+        <v>45323</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         </is>
       </c>
       <c r="I305" t="n">
-        <v>6.6</v>
+        <v>8.9</v>
       </c>
       <c r="J305" t="n">
         <v>0</v>
@@ -24152,24 +24152,24 @@
     <row r="306" ht="15" customHeight="1">
       <c r="A306" t="inlineStr">
         <is>
-          <t>A 19553-2024</t>
+          <t>S 640-2024</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D306" s="1" t="n">
-        <v>45429</v>
+        <v>45355</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         </is>
       </c>
       <c r="I306" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="J306" t="n">
         <v>0</v>
@@ -24225,24 +24225,24 @@
     <row r="307" ht="15" customHeight="1">
       <c r="A307" t="inlineStr">
         <is>
-          <t>A 35003-2025</t>
+          <t>S 1657-2024</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D307" s="1" t="n">
-        <v>45850</v>
+        <v>45429</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         </is>
       </c>
       <c r="I307" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J307" t="n">
         <v>0</v>
@@ -24298,24 +24298,24 @@
     <row r="308" ht="15" customHeight="1">
       <c r="A308" t="inlineStr">
         <is>
-          <t>A 59292-2023</t>
+          <t>S 3691-2024</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D308" s="1" t="n">
-        <v>45253</v>
+        <v>45552</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24371,24 +24371,24 @@
     <row r="309" ht="15" customHeight="1">
       <c r="A309" t="inlineStr">
         <is>
-          <t>A 35004-2025</t>
+          <t>S 4831-2022</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D309" s="1" t="n">
-        <v>45850</v>
+        <v>44804</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         </is>
       </c>
       <c r="I309" t="n">
-        <v>0.6</v>
+        <v>5.9</v>
       </c>
       <c r="J309" t="n">
         <v>0</v>
@@ -24444,24 +24444,24 @@
     <row r="310" ht="15" customHeight="1">
       <c r="A310" t="inlineStr">
         <is>
-          <t>A 17550-2025</t>
+          <t>S 278-2024</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D310" s="1" t="n">
-        <v>45757</v>
+        <v>45323</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         </is>
       </c>
       <c r="I310" t="n">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="J310" t="n">
         <v>0</v>
@@ -24517,7 +24517,7 @@
     <row r="311" ht="15" customHeight="1">
       <c r="A311" t="inlineStr">
         <is>
-          <t>S 277-2024</t>
+          <t>S 639-2024</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -24531,10 +24531,10 @@
         </is>
       </c>
       <c r="D311" s="1" t="n">
-        <v>45323</v>
+        <v>45355</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24547,7 +24547,7 @@
         </is>
       </c>
       <c r="I311" t="n">
-        <v>60.2</v>
+        <v>4.6</v>
       </c>
       <c r="J311" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
     <row r="312" ht="15" customHeight="1">
       <c r="A312" t="inlineStr">
         <is>
-          <t>S 276-2024</t>
+          <t>S 1784-2025</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -24600,14 +24600,14 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D312" s="1" t="n">
-        <v>45323</v>
+        <v>45813</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24620,7 +24620,7 @@
         </is>
       </c>
       <c r="I312" t="n">
-        <v>8.9</v>
+        <v>0.1</v>
       </c>
       <c r="J312" t="n">
         <v>0</v>
@@ -24660,10 +24660,10 @@
       </c>
       <c r="V312" s="2" t="inlineStr"/>
     </row>
-    <row r="313" ht="15" customHeight="1">
+    <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>S 640-2024</t>
+          <t>S 1043-2023</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -24673,14 +24673,14 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D313" s="1" t="n">
-        <v>45355</v>
+        <v>45010</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         </is>
       </c>
       <c r="I313" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J313" t="n">
         <v>0</v>
@@ -24732,517 +24732,6 @@
         <v>0</v>
       </c>
       <c r="V313" s="2" t="inlineStr"/>
-    </row>
-    <row r="314" ht="15" customHeight="1">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>S 1657-2024</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D314" s="1" t="n">
-        <v>45429</v>
-      </c>
-      <c r="E314" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>ALINGSÅS</t>
-        </is>
-      </c>
-      <c r="I314" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J314" t="n">
-        <v>0</v>
-      </c>
-      <c r="K314" t="n">
-        <v>0</v>
-      </c>
-      <c r="L314" t="n">
-        <v>0</v>
-      </c>
-      <c r="M314" t="n">
-        <v>0</v>
-      </c>
-      <c r="N314" t="n">
-        <v>0</v>
-      </c>
-      <c r="O314" t="n">
-        <v>0</v>
-      </c>
-      <c r="P314" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
-      <c r="R314" t="n">
-        <v>0</v>
-      </c>
-      <c r="S314" t="n">
-        <v>0</v>
-      </c>
-      <c r="T314" t="n">
-        <v>0</v>
-      </c>
-      <c r="U314" t="n">
-        <v>0</v>
-      </c>
-      <c r="V314" s="2" t="inlineStr"/>
-    </row>
-    <row r="315" ht="15" customHeight="1">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>S 3691-2024</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D315" s="1" t="n">
-        <v>45552</v>
-      </c>
-      <c r="E315" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>ALINGSÅS</t>
-        </is>
-      </c>
-      <c r="I315" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J315" t="n">
-        <v>0</v>
-      </c>
-      <c r="K315" t="n">
-        <v>0</v>
-      </c>
-      <c r="L315" t="n">
-        <v>0</v>
-      </c>
-      <c r="M315" t="n">
-        <v>0</v>
-      </c>
-      <c r="N315" t="n">
-        <v>0</v>
-      </c>
-      <c r="O315" t="n">
-        <v>0</v>
-      </c>
-      <c r="P315" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q315" t="n">
-        <v>0</v>
-      </c>
-      <c r="R315" t="n">
-        <v>0</v>
-      </c>
-      <c r="S315" t="n">
-        <v>0</v>
-      </c>
-      <c r="T315" t="n">
-        <v>0</v>
-      </c>
-      <c r="U315" t="n">
-        <v>0</v>
-      </c>
-      <c r="V315" s="2" t="inlineStr"/>
-    </row>
-    <row r="316" ht="15" customHeight="1">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>S 4831-2022</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D316" s="1" t="n">
-        <v>44804</v>
-      </c>
-      <c r="E316" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>ALINGSÅS</t>
-        </is>
-      </c>
-      <c r="I316" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J316" t="n">
-        <v>0</v>
-      </c>
-      <c r="K316" t="n">
-        <v>0</v>
-      </c>
-      <c r="L316" t="n">
-        <v>0</v>
-      </c>
-      <c r="M316" t="n">
-        <v>0</v>
-      </c>
-      <c r="N316" t="n">
-        <v>0</v>
-      </c>
-      <c r="O316" t="n">
-        <v>0</v>
-      </c>
-      <c r="P316" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q316" t="n">
-        <v>0</v>
-      </c>
-      <c r="R316" t="n">
-        <v>0</v>
-      </c>
-      <c r="S316" t="n">
-        <v>0</v>
-      </c>
-      <c r="T316" t="n">
-        <v>0</v>
-      </c>
-      <c r="U316" t="n">
-        <v>0</v>
-      </c>
-      <c r="V316" s="2" t="inlineStr"/>
-    </row>
-    <row r="317" ht="15" customHeight="1">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>S 278-2024</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D317" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="E317" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>ALINGSÅS</t>
-        </is>
-      </c>
-      <c r="I317" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J317" t="n">
-        <v>0</v>
-      </c>
-      <c r="K317" t="n">
-        <v>0</v>
-      </c>
-      <c r="L317" t="n">
-        <v>0</v>
-      </c>
-      <c r="M317" t="n">
-        <v>0</v>
-      </c>
-      <c r="N317" t="n">
-        <v>0</v>
-      </c>
-      <c r="O317" t="n">
-        <v>0</v>
-      </c>
-      <c r="P317" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
-      <c r="R317" t="n">
-        <v>0</v>
-      </c>
-      <c r="S317" t="n">
-        <v>0</v>
-      </c>
-      <c r="T317" t="n">
-        <v>0</v>
-      </c>
-      <c r="U317" t="n">
-        <v>0</v>
-      </c>
-      <c r="V317" s="2" t="inlineStr"/>
-    </row>
-    <row r="318" ht="15" customHeight="1">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>S 639-2024</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D318" s="1" t="n">
-        <v>45355</v>
-      </c>
-      <c r="E318" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>ALINGSÅS</t>
-        </is>
-      </c>
-      <c r="I318" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J318" t="n">
-        <v>0</v>
-      </c>
-      <c r="K318" t="n">
-        <v>0</v>
-      </c>
-      <c r="L318" t="n">
-        <v>0</v>
-      </c>
-      <c r="M318" t="n">
-        <v>0</v>
-      </c>
-      <c r="N318" t="n">
-        <v>0</v>
-      </c>
-      <c r="O318" t="n">
-        <v>0</v>
-      </c>
-      <c r="P318" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
-      <c r="R318" t="n">
-        <v>0</v>
-      </c>
-      <c r="S318" t="n">
-        <v>0</v>
-      </c>
-      <c r="T318" t="n">
-        <v>0</v>
-      </c>
-      <c r="U318" t="n">
-        <v>0</v>
-      </c>
-      <c r="V318" s="2" t="inlineStr"/>
-    </row>
-    <row r="319" ht="15" customHeight="1">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>S 1784-2025</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D319" s="1" t="n">
-        <v>45813</v>
-      </c>
-      <c r="E319" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>ALINGSÅS</t>
-        </is>
-      </c>
-      <c r="I319" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J319" t="n">
-        <v>0</v>
-      </c>
-      <c r="K319" t="n">
-        <v>0</v>
-      </c>
-      <c r="L319" t="n">
-        <v>0</v>
-      </c>
-      <c r="M319" t="n">
-        <v>0</v>
-      </c>
-      <c r="N319" t="n">
-        <v>0</v>
-      </c>
-      <c r="O319" t="n">
-        <v>0</v>
-      </c>
-      <c r="P319" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q319" t="n">
-        <v>0</v>
-      </c>
-      <c r="R319" t="n">
-        <v>0</v>
-      </c>
-      <c r="S319" t="n">
-        <v>0</v>
-      </c>
-      <c r="T319" t="n">
-        <v>0</v>
-      </c>
-      <c r="U319" t="n">
-        <v>0</v>
-      </c>
-      <c r="V319" s="2" t="inlineStr"/>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>S 1043-2023</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D320" s="1" t="n">
-        <v>45010</v>
-      </c>
-      <c r="E320" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>ALINGSÅS</t>
-        </is>
-      </c>
-      <c r="I320" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J320" t="n">
-        <v>0</v>
-      </c>
-      <c r="K320" t="n">
-        <v>0</v>
-      </c>
-      <c r="L320" t="n">
-        <v>0</v>
-      </c>
-      <c r="M320" t="n">
-        <v>0</v>
-      </c>
-      <c r="N320" t="n">
-        <v>0</v>
-      </c>
-      <c r="O320" t="n">
-        <v>0</v>
-      </c>
-      <c r="P320" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
-      <c r="R320" t="n">
-        <v>0</v>
-      </c>
-      <c r="S320" t="n">
-        <v>0</v>
-      </c>
-      <c r="T320" t="n">
-        <v>0</v>
-      </c>
-      <c r="U320" t="n">
-        <v>0</v>
-      </c>
-      <c r="V320" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ALINGSÅS.xlsx
+++ b/Översikt ALINGSÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46036</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45091</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45243</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45249</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45630</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44621</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44868</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>45274</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>44803</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>46275</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>45442</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>45630</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45274</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>45240</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>46174</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>46189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>46275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45607</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>46044</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>45279</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45630</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>46245</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45271</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45607</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>46044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45889</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45366</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>46108</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>45812</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>45483</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>45541</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>45330</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>45640</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>44628</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>44614</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44831</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>44754</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>44637</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>44708</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>44817</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>44773</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>44516</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>44852</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>44809</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>44572</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>44652</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>44510</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>44515</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>44496</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>44536</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>44568</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>44809</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>44582</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>44719</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>44795</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>44642</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>44726</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>45378</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45687</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>45406</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>45219</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>45399</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>44855</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>45380</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>45257</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>44832</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>44903</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>45468</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>44896</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>46014</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>45708</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>45708</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>45465</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>46014</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>45271</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>45465</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>45465</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>45465</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>44964</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         <v>45681</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>44957</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>45244</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>45258</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>45510</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>45782</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>46035</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>46038</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>46038</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>45534</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>45894</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>46038</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>46038</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>45576</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>46044</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>45894</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>45901</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>45329</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>45908</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>45908</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>45908</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>45905</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>45910</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>45804</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>45803</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>45916</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>45922</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>46070</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>45804</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>44615</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>45569</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>45929</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>45568</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>45931</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>45805</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>45617</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>45721</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>45634</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>45734</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>45378</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>45279</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>46086</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>46086</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>45279</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>45279</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>44672</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>44672</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>45230</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45937</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45938</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>45937</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>45722</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44637</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>45922</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>46108</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>46108</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>46108</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45958</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>45958</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>45015</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>44505</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>46121</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>46121</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>45964</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>45091</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>45964</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>46122</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>45964</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>44991</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>45966</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>45812</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>45966</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>46127</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45972</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>45972</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45969</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>46126</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>45974</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>45973</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>45973</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>46129</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>45011</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44721</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>44964</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>46131</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>45512</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>45986</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>44727</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>45785</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>45989</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14591,7 +14591,7 @@
         <v>45015</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>45989</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>45706</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44708</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>45660</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>45841</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>45681</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>45996</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>46000</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>45818</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>45915</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>46000</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>45021</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>46008</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>45772</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>45826</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>45699</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>45681</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45792</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>45177</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45726</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>45721</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>45716</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>44977</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45726</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>45726</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45726</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>45465</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>44977</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>45391</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>45596</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>45156</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>45111</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>44949</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>44949</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>45429</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>45850</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>45253</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45850</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>45257</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>46171</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>45335</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>45335</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>45757</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>46174</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>45589</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>46174</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>45133</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>46174</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>46177</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>46177</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>46176</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>46177</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>46177</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>44488</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>46178</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>44631</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>45617</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>46185</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>46189</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>46189</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45637</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>46191</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>46191</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>45576</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>45075</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>44596</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>45329</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>44582</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>45594</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45173</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>45440</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>46255</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45456</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>46262</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45254</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>44727</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>44852</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>45420</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45166</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>46266</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>45465</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>45261</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>45258</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>45271</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45310</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>45265</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>44974</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45210</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>44729</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44831</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>45349</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>44821</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>46232</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>46282</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>45097</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>46245</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>44979</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>46245</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>44896</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>46248</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>46248</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>46289</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>45356</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>45608</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>45608</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>46289</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>44907</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>45546</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>46246</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>44979</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>45196</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>45118</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>44469</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>45679</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>45412</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>45608</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>44953</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>45152</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>44816</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>45166</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>45630</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>44984</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>45608</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44991</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>45600</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>45371</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>45429</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>45427</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>45519</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>45792</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>45323</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45323</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>45355</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45429</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45552</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44804</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>45323</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>45355</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>45813</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>45010</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>

--- a/Översikt ALINGSÅS.xlsx
+++ b/Översikt ALINGSÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46036</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45091</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45243</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45249</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45630</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44621</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44868</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>45274</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>44803</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>46275</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>45442</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>45630</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45274</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>45240</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>46174</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>46189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>46275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45607</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>46044</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>45279</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45630</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>46245</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45271</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45607</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>46044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45889</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45366</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>46108</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>45812</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>45483</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>45541</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>45330</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>45640</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>44628</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>44614</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44831</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>44754</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>44637</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>44708</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>44817</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>44773</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>44516</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>44852</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>44809</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>44572</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>44652</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>44510</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>44515</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>44496</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>44536</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>44568</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>44809</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>44582</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>44719</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>44795</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>44642</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>44726</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>45378</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45687</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>45406</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>45219</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>45399</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>44855</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>45380</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>45257</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>44832</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>44903</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>45468</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>44896</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>46014</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>45708</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>45708</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>45465</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>46014</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>45271</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>45465</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>45465</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>45465</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>44964</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         <v>45681</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>44957</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>45244</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>45258</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>45510</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>45782</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>46035</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>46038</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>46038</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>45534</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>45894</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>46038</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>46038</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>45576</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>46044</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>45894</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>45901</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>45329</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>45908</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>45908</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>45908</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>45905</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>45910</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>45804</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>45803</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>45916</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>45922</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>46070</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>45804</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>44615</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>45569</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>45929</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>45568</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>45931</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>45805</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>45617</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>45721</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>45634</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>45734</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>45378</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>45279</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>46086</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>46086</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>45279</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>45279</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>44672</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>44672</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>45230</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45937</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45938</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>45937</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>45722</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44637</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>45922</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>46108</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>46108</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>46108</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45958</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>45958</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>45015</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>44505</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>46121</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>46121</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>45964</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>45091</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>45964</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>46122</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>45964</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>44991</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>45966</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>45812</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>45966</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>46127</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45972</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>45972</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45969</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>46126</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>45974</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>45973</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>45973</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>46129</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>45011</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44721</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>44964</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>46131</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>45512</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>45986</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>44727</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>45785</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>45989</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14591,7 +14591,7 @@
         <v>45015</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>45989</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>45706</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44708</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>45660</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>45841</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>45681</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>45996</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>46000</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>45818</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>45915</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>46000</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>45021</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>46008</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>45772</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>45826</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>45699</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>45681</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45792</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>45177</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45726</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>45721</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>45716</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>44977</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45726</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>45726</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45726</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>45465</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>44977</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>45391</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>45596</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>45156</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>45111</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>44949</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>44949</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>45429</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>45850</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>45253</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45850</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>45257</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>46171</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>45335</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>45335</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>45757</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>46174</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>45589</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>46174</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>45133</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>46174</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>46177</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>46177</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>46176</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>46177</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>46177</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>44488</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>46178</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>44631</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>45617</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>46185</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>46189</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>46189</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45637</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>46191</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>46191</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>45576</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>45075</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>44596</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>45329</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>44582</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>45594</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45173</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>45440</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>46255</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45456</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>46262</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45254</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>44727</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>44852</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>45420</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45166</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>46266</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>45465</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>45261</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>45258</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>45271</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45310</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>45265</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>44974</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45210</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>44729</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44831</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>45349</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>44821</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>46232</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>46282</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>45097</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>46245</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>44979</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>46245</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>44896</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>46248</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>46248</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>46289</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>45356</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>45608</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>45608</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>46289</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>44907</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>45546</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>46246</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>44979</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>45196</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>45118</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>44469</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>45679</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>45412</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>45608</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>44953</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>45152</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>44816</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>45166</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>45630</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>44984</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>45608</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44991</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>45600</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>45371</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>45429</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>45427</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>45519</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>45792</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>45323</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45323</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>45355</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45429</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45552</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44804</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>45323</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>45355</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>45813</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>45010</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>

--- a/Översikt ALINGSÅS.xlsx
+++ b/Översikt ALINGSÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46036</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45091</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45243</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45249</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45630</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44621</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44868</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45274</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>45279</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>44803</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>46275</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>45274</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>45630</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>45240</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>46189</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>45442</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>46275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>46044</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>45607</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>45279</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45630</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>46245</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45483</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>45889</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>46044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45640</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>45366</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>46108</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>45812</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>45271</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>45330</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45607</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>45541</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>44831</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>44628</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44614</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>44754</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>44637</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>44708</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>44817</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>44516</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>44773</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>44852</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>44809</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>44572</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>44652</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>44510</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>44515</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>44496</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>44536</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>44568</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>44809</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>44582</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>44719</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>44795</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>44642</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>44726</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>45634</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45456</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>44979</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>45118</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>44903</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>44991</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>44582</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>45210</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>45465</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>45617</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>45660</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>45637</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>45015</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>45576</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>45097</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>45782</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>45329</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>45608</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>45608</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>46008</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>45568</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>45465</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         <v>46014</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>46014</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>45708</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>45708</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>45699</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>45894</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>45254</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>45534</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>45894</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>46035</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>45901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>45905</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>46038</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>45792</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>46038</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>46038</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>46038</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>45908</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>45908</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>45908</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>45910</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>45335</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>45335</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>46044</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>45679</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>45916</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>45681</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>45510</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>45258</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>45803</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>45805</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>45111</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>45804</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>45804</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>45922</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>44631</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>45196</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>44991</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>44977</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>45929</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>45406</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>45931</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>45279</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>44672</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>44672</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>45279</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>45279</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>44488</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45937</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45937</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>45938</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>46070</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>45722</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>45617</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>45922</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>45687</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>45734</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45378</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>45261</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>44949</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>45356</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>46086</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>46086</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>45812</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>45958</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>44505</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>45964</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>45964</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>45964</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>45230</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>44727</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>45966</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45966</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45969</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>45972</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45512</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>45972</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>45974</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>45973</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>45973</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>45818</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>46108</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
         <v>46108</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>46108</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>45681</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>45329</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>45986</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>45785</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>45989</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>45989</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14591,7 +14591,7 @@
         <v>45468</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>45721</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>46122</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>46121</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>44979</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>46121</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>45726</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>45726</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>44896</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>45726</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>46126</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>45726</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>45716</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>45996</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>46129</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15696,7 +15696,7 @@
         <v>46127</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>46000</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>46000</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
         <v>46131</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>45219</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45465</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>45465</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>44896</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>45133</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45429</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>45850</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>44984</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>44974</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45253</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>45792</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>45850</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>44596</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>45915</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>45244</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>45826</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>45772</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>45600</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>45681</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>45757</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>45257</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>44615</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>44832</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>44729</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>45841</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>45371</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>45427</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>45412</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>45310</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>44821</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>45420</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45380</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>45596</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>44727</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>45257</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>46174</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>46174</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>46171</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>44721</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>46174</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>45265</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>46176</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19054,7 +19054,7 @@
         <v>46177</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>44964</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>46177</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>46177</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>46177</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>46178</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>45399</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>46185</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>45589</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>44831</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>44708</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>45075</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>46189</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         <v>46189</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         <v>46191</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         <v>46191</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>44957</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
         <v>45608</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>45021</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>45271</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>44852</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45166</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>44964</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45391</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>45152</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>44953</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>46262</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>46266</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21098,7 +21098,7 @@
         <v>45569</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>45378</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>44855</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21317,7 +21317,7 @@
         <v>46232</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>46282</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>45349</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>45091</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>45546</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>45576</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>46245</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>46246</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>45011</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>44907</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22047,7 +22047,7 @@
         <v>44637</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>46289</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>46245</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>45608</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>46290</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22412,7 +22412,7 @@
         <v>46248</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>46248</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>45156</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>46290</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>45465</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>45630</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>46290</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>44949</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>46289</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>45440</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45271</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>45015</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>44977</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>45258</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>46294</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>45166</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>46296</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>46255</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>44816</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>46296</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>46296</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>46296</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>45173</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>45706</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>45465</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45429</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>45177</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45594</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45721</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>45519</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>45323</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>45323</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>45355</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>45429</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>45552</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>44804</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25045,7 +25045,7 @@
         <v>45323</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>45355</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>45813</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>45010</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>

--- a/Översikt ALINGSÅS.xlsx
+++ b/Översikt ALINGSÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46036</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45091</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45243</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45249</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45630</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44621</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44868</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45274</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>45279</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>44803</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>46275</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>45274</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>45630</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>45240</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>46189</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>45442</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>46275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>46044</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>45607</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>45279</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45630</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>46245</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45483</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>45889</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>46044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45640</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>45366</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>46108</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>45812</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>45271</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>45330</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45607</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>45541</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>44831</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>44628</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44614</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>44754</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>44637</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>44708</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>44817</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>44516</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>44773</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>44852</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>44809</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>44572</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>44652</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>44510</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>44515</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>44496</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>44536</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>44568</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>44809</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>44582</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>44719</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>44795</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>44642</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>44726</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>45634</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45456</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>44979</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>45118</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>44903</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>44991</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>44582</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>45210</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>45465</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>45617</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>45660</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>45637</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>45015</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>45576</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>45097</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>45782</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>45329</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>45608</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>45608</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>46008</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>45568</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>45465</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         <v>46014</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>46014</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>45708</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>45708</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>45699</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>45894</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>45254</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>45534</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>45894</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>46035</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>45901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>45905</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>46038</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>45792</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>46038</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>46038</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>46038</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>45908</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>45908</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>45908</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>45910</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>45335</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>45335</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>46044</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>45679</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>45916</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>45681</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>45510</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>45258</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>45803</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>45805</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>45111</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>45804</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>45804</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>45922</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>44631</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>45196</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>44991</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>44977</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>45929</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>45406</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>45931</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>45279</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>44672</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>44672</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>45279</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>45279</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>44488</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45937</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45937</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>45938</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>46070</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>45722</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>45617</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>45922</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>45687</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>45734</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45378</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>45261</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>44949</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>45356</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>46086</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>46086</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>45812</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>45958</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>44505</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>45964</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>45964</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>45964</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>45230</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>44727</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>45966</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45966</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45969</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>45972</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45512</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>45972</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>45974</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>45973</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>45973</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>45818</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>46108</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
         <v>46108</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>46108</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>45681</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>45329</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>45986</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>45785</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>45989</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>45989</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14591,7 +14591,7 @@
         <v>45468</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>45721</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>46122</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>46121</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>44979</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>46121</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>45726</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>45726</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>44896</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>45726</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>46126</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>45726</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>45716</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>45996</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>46129</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15696,7 +15696,7 @@
         <v>46127</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>46000</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>46000</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
         <v>46131</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>45219</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45465</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>45465</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>44896</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>45133</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45429</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>45850</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>44984</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>44974</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45253</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>45792</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>45850</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>44596</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>45915</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>45244</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>45826</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>45772</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>45600</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>45681</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>45757</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>45257</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>44615</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>44832</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>44729</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>45841</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>45371</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>45427</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>45412</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>45310</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>44821</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>45420</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45380</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>45596</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>44727</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>45257</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>46174</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>46174</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>46171</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>44721</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>46174</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>45265</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>46176</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19054,7 +19054,7 @@
         <v>46177</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>44964</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>46177</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>46177</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>46177</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>46178</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>45399</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>46185</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>45589</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>44831</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>44708</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>45075</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>46189</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         <v>46189</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         <v>46191</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         <v>46191</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>44957</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
         <v>45608</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>45021</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>45271</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>44852</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45166</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>44964</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45391</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>45152</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>44953</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>46262</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>46266</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21098,7 +21098,7 @@
         <v>45569</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>45378</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>44855</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21317,7 +21317,7 @@
         <v>46232</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>46282</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>45349</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>45091</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>45546</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>45576</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>46245</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>46246</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>45011</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>44907</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22047,7 +22047,7 @@
         <v>44637</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>46289</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>46245</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>45608</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>46290</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22412,7 +22412,7 @@
         <v>46248</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>46248</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>45156</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>46290</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>45465</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>45630</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>46290</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>44949</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>46289</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>45440</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45271</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>45015</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>44977</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>45258</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>46294</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>45166</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>46296</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>46255</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>44816</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>46296</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>46296</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>46296</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>45173</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>45706</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>45465</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45429</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>45177</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45594</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45721</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>45519</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>45323</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>45323</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>45355</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>45429</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>45552</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>44804</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25045,7 +25045,7 @@
         <v>45323</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>45355</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>45813</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>45010</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>

--- a/Översikt ALINGSÅS.xlsx
+++ b/Översikt ALINGSÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46036</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45091</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45243</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45249</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45630</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44621</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44868</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>45274</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>44803</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>46275</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>45442</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>45630</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45274</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>45240</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>46174</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>46189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>46275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45607</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>45279</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45630</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>46044</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>46245</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45271</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45607</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>45889</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45541</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45366</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>45483</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>46108</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>45812</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>45330</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>46044</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>45640</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>46246</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>44530</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44628</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>44614</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44754</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>44831</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>44637</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>44708</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>44817</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>44516</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>44852</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>44773</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>44809</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>44572</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>44795</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>44652</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>44568</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>44809</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44642</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>44510</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>44582</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>44515</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44496</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>44536</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>44550</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>44719</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>45378</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>44726</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>45406</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>44977</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>45412</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>45608</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45219</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>44953</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>44832</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>45687</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>45399</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>45152</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>45391</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>44816</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>45166</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>45156</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>44855</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>45380</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>45630</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45111</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>44949</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>44949</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         <v>45257</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>44984</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>45608</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>45257</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>44903</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>45468</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>44896</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>44991</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44964</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>45465</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>45271</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>45465</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>45465</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>45465</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>44957</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>45782</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>45335</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>45335</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>45244</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>45589</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>45133</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>45600</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>45894</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>45894</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>45901</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>45371</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>45429</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>45427</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>45534</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>45576</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>45908</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>45908</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         <v>45908</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>45910</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>44488</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>45329</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>44631</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>45617</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>45916</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>45519</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>45922</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>45637</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>44615</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>45576</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>45075</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>44596</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>45329</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>45569</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>45792</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>45929</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>44582</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>45568</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>45681</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>45931</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>45721</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12048,7 +12048,7 @@
         <v>45634</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12121,7 +12121,7 @@
         <v>45594</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>45258</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         <v>45510</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>45279</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>45173</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>45230</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>44637</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>45279</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>45279</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>45804</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>45803</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>44672</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>44672</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>45804</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>45937</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>45805</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>45938</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>45937</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>45617</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>45734</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
         <v>45722</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>45378</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
         <v>45440</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13815,7 +13815,7 @@
         <v>45922</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>45812</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>45015</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>45818</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>44505</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>45091</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>44991</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>45726</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>45721</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>45716</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45726</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>45726</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>45456</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45726</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>45958</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>45254</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>45011</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>44721</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>44964</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>45964</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45964</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>45964</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>44727</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>45966</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45512</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>45966</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>44852</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>45420</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>45972</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>45972</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>44727</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>45969</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>45015</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>45429</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>45166</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>45850</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>45974</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>45706</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>45253</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>45973</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>44708</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45973</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>45660</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>45850</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45757</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>45465</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45261</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>45258</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>45271</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>45021</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>45310</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>45265</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>44974</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>45210</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>44729</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44831</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>45681</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>45349</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>44821</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>45986</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>45177</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44977</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>45097</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>46108</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>46108</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>46108</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>45465</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>45785</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>45989</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>45989</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>46121</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>46121</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>46122</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>45996</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>46127</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>46000</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>46000</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>46126</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>46129</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>46131</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44979</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>44896</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>46008</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45356</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>45608</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45608</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20113,7 +20113,7 @@
         <v>45841</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>45699</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>46014</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>45708</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>45708</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>46014</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>44907</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>45681</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>45546</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45915</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45772</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>46035</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>46038</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>46038</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>44979</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>46038</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>46038</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>45826</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45196</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>46044</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21573,7 +21573,7 @@
         <v>45792</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>45118</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>45679</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>46070</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>46086</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>46086</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>45596</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>46171</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>46174</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>46174</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22303,7 +22303,7 @@
         <v>46174</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         <v>46177</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         <v>46177</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>46176</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>46177</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>46177</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22741,7 +22741,7 @@
         <v>46178</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>46185</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>46189</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>46189</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>46191</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>46191</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>46266</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>46232</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>46282</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>46245</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>46245</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>46289</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>46248</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>46248</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>46290</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>46290</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>46290</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>46296</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>46296</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>46296</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>46289</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>46294</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>46299</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>46255</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>46300</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>45905</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>46296</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>46302</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>46302</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>46262</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45323</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>45323</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45355</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>45429</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>45552</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>44804</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>45323</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>45355</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>45813</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45010</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>

--- a/Översikt ALINGSÅS.xlsx
+++ b/Översikt ALINGSÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46036</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45091</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45243</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45249</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45630</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44621</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44868</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>45274</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>44803</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>46275</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>45442</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>45630</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45274</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>45240</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>46174</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>46189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>46275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45607</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>45279</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45630</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>46044</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>46245</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45271</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45607</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>45889</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45541</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45366</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>45483</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>46108</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>45812</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>45330</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>46044</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>45640</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>46246</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>44530</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44628</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>44614</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44754</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>44831</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>44637</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>44708</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>44817</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>44516</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>44852</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>44773</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>44809</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>44572</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>44795</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>44652</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>44568</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>44809</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44642</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>44510</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>44582</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>44515</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44496</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>44536</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>44550</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>44719</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>45378</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>44726</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>45406</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>44977</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>45412</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>45608</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45219</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>44953</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>44832</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>45687</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>45399</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>45152</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>45391</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>44816</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>45166</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>45156</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>44855</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>45380</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>45630</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45111</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>44949</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>44949</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         <v>45257</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>44984</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>45608</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>45257</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>44903</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>45468</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>44896</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>44991</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44964</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>45465</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>45271</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>45465</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>45465</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>45465</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>44957</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>45782</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>45335</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>45335</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>45244</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>45589</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>45133</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>45600</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>45894</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>45894</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>45901</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>45371</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>45429</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>45427</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>45534</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>45576</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>45908</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>45908</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         <v>45908</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>45910</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>44488</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>45329</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>44631</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>45617</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>45916</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>45519</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>45922</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>45637</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>44615</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>45576</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>45075</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>44596</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>45329</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>45569</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>45792</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>45929</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>44582</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>45568</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>45681</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>45931</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>45721</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12048,7 +12048,7 @@
         <v>45634</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12121,7 +12121,7 @@
         <v>45594</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>45258</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         <v>45510</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>45279</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>45173</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>45230</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>44637</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>45279</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>45279</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>45804</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>45803</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>44672</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>44672</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>45804</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>45937</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>45805</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>45938</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>45937</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>45617</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>45734</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
         <v>45722</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>45378</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
         <v>45440</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13815,7 +13815,7 @@
         <v>45922</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>45812</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>45015</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>45818</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>44505</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>45091</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>44991</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>45726</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>45721</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>45716</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45726</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>45726</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>45456</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45726</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>45958</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>45254</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>45011</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>44721</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>44964</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>45964</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45964</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>45964</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>44727</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>45966</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45512</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>45966</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>44852</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>45420</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>45972</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>45972</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>44727</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>45969</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>45015</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>45429</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>45166</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>45850</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>45974</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>45706</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>45253</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>45973</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>44708</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45973</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>45660</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>45850</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45757</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>45465</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45261</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>45258</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>45271</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>45021</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>45310</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>45265</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>44974</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>45210</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>44729</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44831</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>45681</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>45349</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>44821</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>45986</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>45177</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44977</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>45097</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>46108</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>46108</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>46108</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>45465</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>45785</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>45989</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>45989</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>46121</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>46121</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>46122</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>45996</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>46127</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>46000</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>46000</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>46126</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>46129</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>46131</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44979</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>44896</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>46008</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45356</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>45608</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45608</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20113,7 +20113,7 @@
         <v>45841</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>45699</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>46014</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>45708</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>45708</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>46014</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>44907</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>45681</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>45546</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45915</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45772</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>46035</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>46038</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>46038</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>44979</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>46038</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>46038</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>45826</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45196</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>46044</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21573,7 +21573,7 @@
         <v>45792</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>45118</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>45679</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>46070</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>46086</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>46086</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>45596</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>46171</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>46174</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>46174</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22303,7 +22303,7 @@
         <v>46174</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         <v>46177</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         <v>46177</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>46176</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>46177</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>46177</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22741,7 +22741,7 @@
         <v>46178</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>46185</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>46189</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>46189</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>46191</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>46191</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>46266</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>46232</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>46282</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>46245</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>46245</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>46289</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>46248</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>46248</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>46290</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>46290</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>46290</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>46296</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>46296</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>46296</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>46289</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>46294</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>46299</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>46255</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>46300</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>45905</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>46296</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>46302</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>46302</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>46262</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45323</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>45323</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45355</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>45429</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>45552</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>44804</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>45323</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>45355</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>45813</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45010</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>

--- a/Översikt ALINGSÅS.xlsx
+++ b/Översikt ALINGSÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46036</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45091</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45243</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45249</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45630</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44621</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44868</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45274</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>45279</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>44803</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>46275</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>45274</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>45630</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>45240</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>46189</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>45442</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>46275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45279</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45630</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>46044</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>46245</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45607</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45483</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>45640</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>45889</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>45271</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45812</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>45330</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>46044</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>46108</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>46246</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45607</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>45541</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>45366</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>44530</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44628</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>44614</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44831</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>44754</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>44637</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>44708</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>44817</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>44773</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>44516</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>44852</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>44809</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>44572</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>44652</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>44510</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>44515</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>44496</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44536</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>44550</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>44568</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>44809</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44582</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>44719</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>44795</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>44642</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>44726</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>45634</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>44979</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>45456</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>45118</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>44903</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>44991</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44582</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>45210</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>45660</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>45465</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>45637</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>45617</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>45576</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>45097</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>45015</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>45329</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>45608</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>45608</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45568</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>45465</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>45254</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         <v>45534</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>45335</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>45335</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>45679</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>45111</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>45196</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>44991</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44631</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44977</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>45406</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>44488</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>45687</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>45356</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>45261</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>44949</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>44505</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>45230</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         <v>44727</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>45512</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>45681</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>45329</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>45468</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>45792</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>44979</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44896</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>45915</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44964</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>45894</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>45826</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>45772</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>45782</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>45681</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>45219</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>45465</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>45465</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10583,7 +10583,7 @@
         <v>45894</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>45901</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>45841</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10802,7 +10802,7 @@
         <v>44896</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>45908</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>45908</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>45908</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>45910</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>45916</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>45133</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>45922</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>44984</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>44974</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>45929</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>44596</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>45931</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>45279</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>44672</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>44672</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>45279</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>45279</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>45937</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>45937</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>45938</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>45244</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>45722</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>45600</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>45922</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>45257</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>44615</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         <v>45958</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>44832</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12934,7 +12934,7 @@
         <v>44729</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>45964</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>45371</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>45964</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>45964</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>45966</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>45966</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>45596</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>45427</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>45969</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>45972</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>45972</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>45412</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>45974</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45973</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45973</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45310</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>44821</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>45986</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>45420</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>45785</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>45989</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>45989</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>45380</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>45996</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>46000</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>46000</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>44727</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>46174</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45257</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>46174</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>46171</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>46008</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>44721</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>45265</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>46174</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>46014</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>46014</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>45708</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>45708</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>45699</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>45399</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>46035</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>46176</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>46177</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>46038</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>46038</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>46038</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>46038</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>46177</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>46177</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>46177</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>46178</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45589</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>44831</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>44708</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>46044</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>45075</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>44957</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>45608</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>45021</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>45271</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>46070</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>44852</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>45166</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>46185</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>46086</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>46086</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44964</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>45391</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>46189</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>46189</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>45152</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>46191</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>46191</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>44953</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>46108</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>46108</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>46108</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>46122</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>46121</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>46121</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>46126</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>46129</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>46127</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>45569</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>46131</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>45378</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>44855</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>45349</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>45091</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>45546</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>45576</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>45011</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>44907</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>44637</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>45608</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>45156</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>45465</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>46232</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>45630</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>44949</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>45440</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>45271</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>45015</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>44977</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>45258</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
         <v>45166</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>46282</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>44816</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>45173</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>46245</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>46289</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         <v>46245</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>46290</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>46248</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>46248</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>45706</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>46290</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21641,7 +21641,7 @@
         <v>45465</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>46290</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21787,7 +21787,7 @@
         <v>45429</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>46289</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>46294</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>45177</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>46296</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>45594</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>46296</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>46296</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>46296</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>45721</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>46300</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>45905</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>46299</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>46255</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45519</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>46302</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>46302</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>46307</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45792</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>45681</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45510</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>45258</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>46262</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45803</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>45805</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>45804</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>45804</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>46266</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>45617</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>45734</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>45378</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24050,7 +24050,7 @@
         <v>45812</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45818</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>45721</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45726</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>45726</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>45726</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>45726</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>45716</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45429</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45850</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>45253</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>45850</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45757</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>45323</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45323</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>45355</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>45429</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45552</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>44804</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>45323</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>45355</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45813</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>45010</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>

--- a/Översikt ALINGSÅS.xlsx
+++ b/Översikt ALINGSÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46036</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45091</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45243</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45249</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45630</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44621</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44868</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45274</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>45279</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>44803</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>46275</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>45274</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>45630</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>45240</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>46174</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>46189</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>45442</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>46275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45279</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45630</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>46044</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>46245</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45607</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45483</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>45640</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>45889</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>45271</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45812</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>45330</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>46044</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>46108</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>46246</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45607</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>45541</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>45366</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>44530</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44628</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>44614</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44831</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>44754</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>44637</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>44708</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>44817</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>44773</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>44516</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>44852</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>44809</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>44572</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>44652</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>44510</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>44515</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>44496</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44536</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>44550</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>44568</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>44809</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44582</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>44719</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>44795</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>44642</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>44726</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>45634</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>44979</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>45456</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>45118</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>44903</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>44991</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44582</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>45210</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>45660</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>45465</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>45637</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>45617</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>45576</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>45097</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>45015</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>45329</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>45608</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>45608</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45568</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>45465</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>45254</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         <v>45534</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>45335</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>45335</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>45679</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>45111</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>45196</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>44991</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44631</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44977</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>45406</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>44488</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>45687</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>45356</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>45261</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>44949</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>44505</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>45230</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         <v>44727</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>45512</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>45681</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>45329</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>45468</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>45792</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>44979</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44896</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>45915</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44964</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>45894</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>45826</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>45772</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>45782</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>45681</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>45219</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>45465</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>45465</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10583,7 +10583,7 @@
         <v>45894</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>45901</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>45841</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10802,7 +10802,7 @@
         <v>44896</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>45908</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>45908</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>45908</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>45910</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>45916</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>45133</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>45922</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>44984</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>44974</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>45929</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>44596</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>45931</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>45279</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>44672</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>44672</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>45279</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>45279</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>45937</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>45937</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>45938</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>45244</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>45722</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>45600</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>45922</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>45257</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>44615</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         <v>45958</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>44832</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12934,7 +12934,7 @@
         <v>44729</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>45964</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>45371</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>45964</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>45964</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>45966</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>45966</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>45596</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>45427</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>45969</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>45972</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>45972</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>45412</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>45974</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45973</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45973</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45310</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>44821</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>45986</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>45420</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>45785</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>45989</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>45989</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>45380</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>45996</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>46000</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>46000</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>44727</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>46174</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45257</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>46174</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>46171</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>46008</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>44721</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>45265</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>46174</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>46014</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>46014</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>45708</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>45708</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>45699</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>45399</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>46035</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>46176</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>46177</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>46038</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>46038</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>46038</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>46038</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>46177</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>46177</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>46177</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>46178</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45589</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>44831</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>44708</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>46044</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>45075</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>44957</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>45608</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>45021</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>45271</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>46070</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>44852</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>45166</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>46185</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>46086</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>46086</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44964</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>45391</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>46189</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>46189</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>45152</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>46191</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>46191</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>44953</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>46108</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>46108</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>46108</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>46122</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>46121</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>46121</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>46126</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>46129</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>46127</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>45569</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>46131</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>45378</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>44855</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>45349</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>45091</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>45546</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>45576</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>45011</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>44907</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>44637</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>45608</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>45156</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>45465</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>46232</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>45630</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>44949</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>45440</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>45271</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>45015</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>44977</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>45258</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
         <v>45166</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>46282</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>44816</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>45173</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>46245</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>46289</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         <v>46245</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>46290</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>46248</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>46248</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>45706</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>46290</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21641,7 +21641,7 @@
         <v>45465</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>46290</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21787,7 +21787,7 @@
         <v>45429</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>46289</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>46294</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>45177</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>46296</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>45594</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>46296</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>46296</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>46296</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>45721</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>46300</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>45905</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>46299</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>46255</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45519</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>46302</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>46302</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>46307</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45792</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>45681</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45510</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>45258</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>46262</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45803</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>45805</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>45804</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>45804</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>46266</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>45617</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>45734</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>45378</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24050,7 +24050,7 @@
         <v>45812</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45818</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>45721</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45726</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>45726</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>45726</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>45726</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>45716</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45429</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45850</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>45253</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>45850</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45757</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>45323</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45323</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>45355</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>45429</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45552</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>44804</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>45323</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>45355</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45813</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>45010</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>

--- a/Översikt ALINGSÅS.xlsx
+++ b/Översikt ALINGSÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46036</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45091</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45243</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45249</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45630</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44621</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44868</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>45274</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>46275</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>45630</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>45274</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>46174</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>46189</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45442</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>46275</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>45240</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45279</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45630</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>46245</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>46044</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45607</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45889</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45640</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45812</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>45271</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>46044</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>45366</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>46246</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>45607</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>46108</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>45483</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>45541</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45330</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>44530</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44628</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>44614</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44754</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>44831</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>44637</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>44708</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>44817</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>44516</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>44773</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>44852</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>44809</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>44572</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>44652</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>44510</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>44515</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>44536</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44496</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>44550</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>44568</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>44809</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44582</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>44719</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>44795</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>44642</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>44726</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>44979</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>44896</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>45687</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>45782</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>45894</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45356</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>45608</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>45608</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>44964</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>45894</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>45901</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>45378</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>44907</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>45406</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>45546</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>45908</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>45908</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>45908</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>45910</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>45916</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>45922</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>44979</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>45196</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>45929</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>45118</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>45931</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>45219</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>46171</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>45279</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>46174</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>45279</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>45279</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>44672</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>44672</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>45937</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>45938</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>45937</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>44832</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>45722</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>46174</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>45679</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>46174</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>45399</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>46177</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>45412</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>45922</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>46176</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>45608</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>46177</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>44855</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>45380</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>46177</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>44953</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>45257</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>45152</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>46178</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>44816</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>45166</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>45958</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>46185</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>45630</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>45964</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>45964</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>45964</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>46189</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>46189</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>45966</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>44984</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>45966</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>46191</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>46191</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>45972</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>45972</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>45969</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>45974</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11980,7 +11980,7 @@
         <v>45973</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>45973</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>44991</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>45986</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>45600</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12345,7 +12345,7 @@
         <v>45371</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>45785</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>45429</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>45989</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>45427</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>45989</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>44903</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>45468</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>44896</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>45465</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>45996</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
         <v>46000</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>46000</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>46008</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>46232</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         <v>45699</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         <v>46014</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>45708</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>45708</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>45519</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>46014</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>45271</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>45465</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>45465</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>46282</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         <v>45465</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>45792</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>46038</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>45681</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>46038</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>46038</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>46044</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>46245</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45258</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>45510</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>46245</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>45804</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45803</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>45804</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>45805</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>46289</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>45617</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>45734</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>45378</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>44957</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>45812</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>46248</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>46248</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>46290</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>46290</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>46070</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>45818</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>46290</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>45244</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>46296</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>46296</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>46296</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>45726</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>46289</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>45721</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>45716</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>45726</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>45726</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>45726</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>46294</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>46086</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>46086</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>46299</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>46255</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>46300</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>45905</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>46302</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>45429</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>45850</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>45253</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>45850</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>46108</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>46302</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>46108</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>46108</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>45757</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>46121</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>46121</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>46122</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>46127</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>46126</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>46129</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>45534</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>46262</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>46307</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>46131</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>45576</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45329</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>46266</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>45841</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45681</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>45915</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>46314</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>44615</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>46314</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>45772</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         <v>45569</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45826</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>45792</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>46316</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>46316</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>46035</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>46038</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>45568</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>45721</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>45634</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>46296</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>45230</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>44637</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>45015</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
         <v>45596</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>44505</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>45091</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44991</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>45011</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>44721</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         <v>44964</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>45512</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>44727</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>45015</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>45706</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>44708</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21641,7 +21641,7 @@
         <v>45660</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>45021</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21787,7 +21787,7 @@
         <v>45681</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>45177</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>44977</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>45465</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>44977</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>45391</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>45156</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22303,7 +22303,7 @@
         <v>45111</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         <v>44949</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         <v>44949</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>45257</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>45335</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>45335</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22741,7 +22741,7 @@
         <v>45589</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>45133</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>44631</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>45617</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>45637</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>45576</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>45075</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>44596</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>45329</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>44582</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>45594</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>45173</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45440</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>45456</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>45254</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>44727</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>44852</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>45420</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>45166</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>45465</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>45261</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45258</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>45271</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>45310</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>45265</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44974</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45210</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>44729</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>44831</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>45349</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>44821</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>45097</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45323</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>45323</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>45355</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45429</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>45552</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>44804</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>45323</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45355</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>45813</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>45010</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>

--- a/Översikt ALINGSÅS.xlsx
+++ b/Översikt ALINGSÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46036</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45091</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45243</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45249</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45630</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44621</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44868</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>45274</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>46275</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>45630</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>45274</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>46174</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>46189</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45442</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>46275</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>45240</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45279</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45630</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>46245</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>46044</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45607</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45889</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45640</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45812</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>45271</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>46044</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>45366</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>46246</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>45607</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>46108</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>45483</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>45541</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45330</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>44530</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44628</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>44614</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44754</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>44831</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>44637</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>44708</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>44817</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>44516</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>44773</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>44852</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>44809</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>44572</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>44652</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>44510</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>44515</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>44536</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44496</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>44550</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>44568</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>44809</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44582</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>44719</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>44795</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>44642</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>44726</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>44979</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>44896</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>45687</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>45782</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>45894</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45356</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>45608</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>45608</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>44964</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>45894</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>45901</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>45378</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>44907</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>45406</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>45546</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>45908</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>45908</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>45908</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>45910</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>45916</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>45922</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>44979</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>45196</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>45929</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>45118</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>45931</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>45219</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>46171</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>45279</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>46174</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>45279</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>45279</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>44672</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>44672</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>45937</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>45938</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>45937</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>44832</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>45722</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>46174</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>45679</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>46174</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>45399</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>46177</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>45412</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>45922</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>46176</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>45608</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>46177</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>44855</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>45380</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>46177</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>44953</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>45257</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>45152</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>46178</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>44816</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>45166</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>45958</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>46185</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>45630</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>45964</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>45964</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>45964</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>46189</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>46189</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>45966</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>44984</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>45966</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>46191</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>46191</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>45972</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>45972</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>45969</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>45974</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11980,7 +11980,7 @@
         <v>45973</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>45973</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>44991</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>45986</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>45600</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12345,7 +12345,7 @@
         <v>45371</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>45785</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>45429</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>45989</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>45427</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>45989</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>44903</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>45468</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>44896</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>45465</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>45996</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
         <v>46000</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>46000</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>46008</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>46232</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         <v>45699</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         <v>46014</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>45708</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>45708</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>45519</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>46014</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>45271</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>45465</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>45465</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>46282</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         <v>45465</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>45792</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>46038</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>45681</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>46038</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>46038</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>46044</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>46245</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45258</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>45510</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>46245</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>45804</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45803</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>45804</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>45805</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>46289</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>45617</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>45734</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>45378</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>44957</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>45812</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>46248</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>46248</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>46290</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>46290</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>46070</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>45818</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>46290</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>45244</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>46296</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>46296</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>46296</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>45726</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>46289</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>45721</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>45716</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>45726</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>45726</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>45726</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>46294</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>46086</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>46086</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>46299</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>46255</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>46300</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>45905</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>46302</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>45429</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>45850</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>45253</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>45850</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>46108</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>46302</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>46108</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>46108</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>45757</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>46121</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>46121</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>46122</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>46127</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>46126</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>46129</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>45534</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>46262</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>46307</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>46131</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>45576</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45329</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>46266</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>45841</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45681</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>45915</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>46314</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>44615</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>46314</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>45772</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         <v>45569</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45826</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>45792</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>46316</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>46316</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>46035</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>46038</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>45568</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>45721</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>45634</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>46296</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>45230</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>44637</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>45015</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
         <v>45596</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>44505</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>45091</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44991</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>45011</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>44721</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         <v>44964</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>45512</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>44727</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>45015</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>45706</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>44708</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21641,7 +21641,7 @@
         <v>45660</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>45021</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21787,7 +21787,7 @@
         <v>45681</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>45177</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>44977</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>45465</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>44977</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>45391</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>45156</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22303,7 +22303,7 @@
         <v>45111</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         <v>44949</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         <v>44949</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>45257</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>45335</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>45335</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22741,7 +22741,7 @@
         <v>45589</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>45133</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>44631</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>45617</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>45637</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>45576</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>45075</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>44596</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>45329</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>44582</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>45594</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>45173</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45440</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>45456</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>45254</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>44727</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>44852</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>45420</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>45166</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>45465</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>45261</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45258</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>45271</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>45310</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>45265</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44974</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45210</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>44729</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>44831</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>45349</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>44821</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>45097</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45323</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>45323</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>45355</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45429</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>45552</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>44804</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>45323</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45355</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>45813</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>45010</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
